--- a/data/LME_052/LME_052.xlsx
+++ b/data/LME_052/LME_052.xlsx
@@ -131,9 +131,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -506,10 +504,10 @@
   <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" style="13" min="1" max="1"/>
+    <col width="22" customWidth="1" style="13" min="2" max="2"/>
+    <col width="22" customWidth="1" style="13" min="3" max="3"/>
+    <col width="30" customWidth="1" style="13" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,6 +520,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -634,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -1520,21 +1520,21 @@
   <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="75" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-    <col width="65" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" style="13" min="1" max="1"/>
+    <col width="23" customWidth="1" style="13" min="2" max="2"/>
+    <col width="23" customWidth="1" style="13" min="3" max="3"/>
+    <col width="23" customWidth="1" style="13" min="4" max="4"/>
+    <col width="23" customWidth="1" style="13" min="5" max="5"/>
+    <col width="23" customWidth="1" style="13" min="6" max="6"/>
+    <col width="23" customWidth="1" style="13" min="7" max="7"/>
+    <col width="23" customWidth="1" style="13" min="8" max="8"/>
+    <col width="23" customWidth="1" style="13" min="9" max="9"/>
+    <col width="22" customWidth="1" style="13" min="10" max="10"/>
+    <col width="60" customWidth="1" style="13" min="11" max="11"/>
+    <col width="75" customWidth="1" style="13" min="12" max="12"/>
+    <col width="12" customWidth="1" style="13" min="13" max="13"/>
+    <col width="36" customWidth="1" style="13" min="14" max="14"/>
+    <col width="65" customWidth="1" style="13" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="32" customHeight="1" s="13">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>year</t>
@@ -1642,12 +1642,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1663,12 +1660,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1684,12 +1678,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1705,12 +1696,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1726,12 +1714,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1747,12 +1732,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1768,12 +1750,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,12 +1768,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,12 +1786,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1831,12 +1804,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1852,12 +1822,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1873,12 +1840,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1894,12 +1858,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1915,12 +1876,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1936,12 +1894,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1957,12 +1912,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1978,12 +1930,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1999,12 +1948,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2020,12 +1966,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2041,12 +1984,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2062,12 +2002,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2083,12 +2020,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2104,12 +2038,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2125,12 +2056,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2146,12 +2074,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2167,12 +2092,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2188,12 +2110,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2209,12 +2128,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2230,12 +2146,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2251,12 +2164,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2272,12 +2182,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2293,12 +2200,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2314,12 +2218,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2335,12 +2236,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2356,12 +2254,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2377,12 +2272,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2398,12 +2290,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2419,12 +2308,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2440,12 +2326,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2461,12 +2344,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2482,12 +2362,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2503,12 +2380,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2524,12 +2398,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2545,12 +2416,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2566,12 +2434,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2587,12 +2452,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2608,12 +2470,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2629,12 +2488,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2894,7 +2750,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
@@ -2947,7 +2802,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
@@ -3000,7 +2854,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
@@ -3053,7 +2906,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
@@ -3106,7 +2958,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
@@ -3159,7 +3010,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
@@ -3212,7 +3062,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
@@ -3265,7 +3114,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
@@ -3318,7 +3166,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
@@ -3371,7 +3218,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
@@ -3424,7 +3270,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
@@ -3477,7 +3322,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
@@ -3530,7 +3374,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
@@ -3583,7 +3426,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
@@ -3636,7 +3478,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
@@ -3689,7 +3530,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
@@ -3742,7 +3582,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
@@ -3777,80 +3616,80 @@
   <dimension ref="A1:BV152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="14" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="14" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-    <col width="14" customWidth="1" min="63" max="63"/>
-    <col width="14" customWidth="1" min="64" max="64"/>
-    <col width="14" customWidth="1" min="65" max="65"/>
-    <col width="14" customWidth="1" min="66" max="66"/>
-    <col width="14" customWidth="1" min="67" max="67"/>
-    <col width="14" customWidth="1" min="68" max="68"/>
-    <col width="14" customWidth="1" min="69" max="69"/>
-    <col width="14" customWidth="1" min="70" max="70"/>
-    <col width="14" customWidth="1" min="71" max="71"/>
-    <col width="14" customWidth="1" min="72" max="72"/>
-    <col width="14" customWidth="1" min="73" max="73"/>
-    <col width="14" customWidth="1" min="74" max="74"/>
+    <col width="26" customWidth="1" style="13" min="1" max="1"/>
+    <col width="22" customWidth="1" style="13" min="2" max="2"/>
+    <col width="14" customWidth="1" style="13" min="3" max="3"/>
+    <col width="14" customWidth="1" style="13" min="4" max="4"/>
+    <col width="14" customWidth="1" style="13" min="5" max="5"/>
+    <col width="14" customWidth="1" style="13" min="6" max="6"/>
+    <col width="14" customWidth="1" style="13" min="7" max="7"/>
+    <col width="14" customWidth="1" style="13" min="8" max="8"/>
+    <col width="14" customWidth="1" style="13" min="9" max="9"/>
+    <col width="14" customWidth="1" style="13" min="10" max="10"/>
+    <col width="14" customWidth="1" style="13" min="11" max="11"/>
+    <col width="14" customWidth="1" style="13" min="12" max="12"/>
+    <col width="14" customWidth="1" style="13" min="13" max="13"/>
+    <col width="14" customWidth="1" style="13" min="14" max="14"/>
+    <col width="14" customWidth="1" style="13" min="15" max="15"/>
+    <col width="14" customWidth="1" style="13" min="16" max="16"/>
+    <col width="14" customWidth="1" style="13" min="17" max="17"/>
+    <col width="14" customWidth="1" style="13" min="18" max="18"/>
+    <col width="14" customWidth="1" style="13" min="19" max="19"/>
+    <col width="14" customWidth="1" style="13" min="20" max="20"/>
+    <col width="14" customWidth="1" style="13" min="21" max="21"/>
+    <col width="14" customWidth="1" style="13" min="22" max="22"/>
+    <col width="14" customWidth="1" style="13" min="23" max="23"/>
+    <col width="14" customWidth="1" style="13" min="24" max="24"/>
+    <col width="14" customWidth="1" style="13" min="25" max="25"/>
+    <col width="14" customWidth="1" style="13" min="26" max="26"/>
+    <col width="14" customWidth="1" style="13" min="27" max="27"/>
+    <col width="14" customWidth="1" style="13" min="28" max="28"/>
+    <col width="14" customWidth="1" style="13" min="29" max="29"/>
+    <col width="14" customWidth="1" style="13" min="30" max="30"/>
+    <col width="14" customWidth="1" style="13" min="31" max="31"/>
+    <col width="14" customWidth="1" style="13" min="32" max="32"/>
+    <col width="14" customWidth="1" style="13" min="33" max="33"/>
+    <col width="14" customWidth="1" style="13" min="34" max="34"/>
+    <col width="14" customWidth="1" style="13" min="35" max="35"/>
+    <col width="14" customWidth="1" style="13" min="36" max="36"/>
+    <col width="14" customWidth="1" style="13" min="37" max="37"/>
+    <col width="14" customWidth="1" style="13" min="38" max="38"/>
+    <col width="14" customWidth="1" style="13" min="39" max="39"/>
+    <col width="14" customWidth="1" style="13" min="40" max="40"/>
+    <col width="14" customWidth="1" style="13" min="41" max="41"/>
+    <col width="14" customWidth="1" style="13" min="42" max="42"/>
+    <col width="14" customWidth="1" style="13" min="43" max="43"/>
+    <col width="14" customWidth="1" style="13" min="44" max="44"/>
+    <col width="14" customWidth="1" style="13" min="45" max="45"/>
+    <col width="14" customWidth="1" style="13" min="46" max="46"/>
+    <col width="14" customWidth="1" style="13" min="47" max="47"/>
+    <col width="14" customWidth="1" style="13" min="48" max="48"/>
+    <col width="14" customWidth="1" style="13" min="49" max="49"/>
+    <col width="14" customWidth="1" style="13" min="50" max="50"/>
+    <col width="14" customWidth="1" style="13" min="51" max="51"/>
+    <col width="14" customWidth="1" style="13" min="52" max="52"/>
+    <col width="14" customWidth="1" style="13" min="53" max="53"/>
+    <col width="14" customWidth="1" style="13" min="54" max="54"/>
+    <col width="14" customWidth="1" style="13" min="55" max="55"/>
+    <col width="14" customWidth="1" style="13" min="56" max="56"/>
+    <col width="14" customWidth="1" style="13" min="57" max="57"/>
+    <col width="14" customWidth="1" style="13" min="58" max="58"/>
+    <col width="14" customWidth="1" style="13" min="59" max="59"/>
+    <col width="14" customWidth="1" style="13" min="60" max="60"/>
+    <col width="14" customWidth="1" style="13" min="61" max="61"/>
+    <col width="14" customWidth="1" style="13" min="62" max="62"/>
+    <col width="14" customWidth="1" style="13" min="63" max="63"/>
+    <col width="14" customWidth="1" style="13" min="64" max="64"/>
+    <col width="14" customWidth="1" style="13" min="65" max="65"/>
+    <col width="14" customWidth="1" style="13" min="66" max="66"/>
+    <col width="14" customWidth="1" style="13" min="67" max="67"/>
+    <col width="14" customWidth="1" style="13" min="68" max="68"/>
+    <col width="14" customWidth="1" style="13" min="69" max="69"/>
+    <col width="14" customWidth="1" style="13" min="70" max="70"/>
+    <col width="14" customWidth="1" style="13" min="71" max="71"/>
+    <col width="14" customWidth="1" style="13" min="72" max="72"/>
+    <col width="14" customWidth="1" style="13" min="73" max="73"/>
+    <col width="14" customWidth="1" style="13" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39131,19 +38970,19 @@
   <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="95" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" style="13" min="1" max="1"/>
+    <col width="46" customWidth="1" style="13" min="2" max="2"/>
+    <col width="30" customWidth="1" style="13" min="3" max="3"/>
+    <col width="23" customWidth="1" style="13" min="4" max="4"/>
+    <col width="27" customWidth="1" style="13" min="5" max="5"/>
+    <col width="24" customWidth="1" style="13" min="6" max="6"/>
+    <col width="35" customWidth="1" style="13" min="7" max="7"/>
+    <col width="23" customWidth="1" style="13" min="8" max="8"/>
+    <col width="22" customWidth="1" style="13" min="9" max="9"/>
+    <col width="14" customWidth="1" style="13" min="10" max="10"/>
+    <col width="24" customWidth="1" style="13" min="11" max="11"/>
+    <col width="95" customWidth="1" style="13" min="12" max="12"/>
+    <col width="18" customWidth="1" style="13" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39234,7 +39073,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="36" customHeight="1" s="13">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39297,7 +39136,7 @@
         <v>146132008.462</v>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="36" customHeight="1" s="13">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39360,7 +39199,7 @@
         <v>146132008.462</v>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="36" customHeight="1" s="13">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39423,7 +39262,7 @@
         <v>18753775.683</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="36" customHeight="1" s="13">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39486,7 +39325,7 @@
         <v>14223073.136</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="36" customHeight="1" s="13">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39549,7 +39388,7 @@
         <v>14223073.136</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="36" customHeight="1" s="13">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39612,7 +39451,7 @@
         <v>14223073.136</v>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="36" customHeight="1" s="13">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39675,7 +39514,7 @@
         <v>14223073.136</v>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="36" customHeight="1" s="13">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39738,7 +39577,7 @@
         <v>11221364.935</v>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="51" customHeight="1" s="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39801,7 +39640,7 @@
         <v>6361027.532</v>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="36" customHeight="1" s="13">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39864,7 +39703,7 @@
         <v>5161513.421</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="36" customHeight="1" s="13">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39927,7 +39766,7 @@
         <v>3616523.455</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="36" customHeight="1" s="13">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -39990,7 +39829,7 @@
         <v>3266940.097</v>
       </c>
     </row>
-    <row r="17" ht="51" customHeight="1">
+    <row r="17" ht="51" customHeight="1" s="13">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40053,7 +39892,7 @@
         <v>2647805.622</v>
       </c>
     </row>
-    <row r="18" ht="51" customHeight="1">
+    <row r="18" ht="51" customHeight="1" s="13">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40116,7 +39955,7 @@
         <v>2647805.622</v>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="36" customHeight="1" s="13">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40179,7 +40018,7 @@
         <v>2194189.219</v>
       </c>
     </row>
-    <row r="20" ht="51" customHeight="1">
+    <row r="20" ht="51" customHeight="1" s="13">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40242,7 +40081,7 @@
         <v>1970290.649</v>
       </c>
     </row>
-    <row r="21" ht="51" customHeight="1">
+    <row r="21" ht="51" customHeight="1" s="13">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40299,7 +40138,7 @@
         <v>1716358.066</v>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="36" customHeight="1" s="13">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40362,7 +40201,7 @@
         <v>1601595.175</v>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="36" customHeight="1" s="13">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40425,7 +40264,7 @@
         <v>1420067.304</v>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="36" customHeight="1" s="13">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40488,7 +40327,7 @@
         <v>1413151.605</v>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="36" customHeight="1" s="13">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40551,7 +40390,7 @@
         <v>1397772.673</v>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="36" customHeight="1" s="13">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40614,7 +40453,7 @@
         <v>1330721.237</v>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="36" customHeight="1" s="13">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40677,7 +40516,7 @@
         <v>1330721.237</v>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="36" customHeight="1" s="13">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40740,7 +40579,7 @@
         <v>1330721.237</v>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1">
+    <row r="29" ht="36" customHeight="1" s="13">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40797,7 +40636,7 @@
         <v>1247073.954</v>
       </c>
     </row>
-    <row r="30" ht="51" customHeight="1">
+    <row r="30" ht="51" customHeight="1" s="13">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40860,7 +40699,7 @@
         <v>1245166.946</v>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1">
+    <row r="31" ht="36" customHeight="1" s="13">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40923,7 +40762,7 @@
         <v>1182462.308</v>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" ht="36" customHeight="1" s="13">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -40986,7 +40825,7 @@
         <v>1084818.657</v>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
+    <row r="33" ht="36" customHeight="1" s="13">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41049,7 +40888,7 @@
         <v>1077371.301</v>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
+    <row r="34" ht="36" customHeight="1" s="13">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41112,7 +40951,7 @@
         <v>935887.171</v>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
+    <row r="35" ht="36" customHeight="1" s="13">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41169,7 +41008,7 @@
         <v>883031.144</v>
       </c>
     </row>
-    <row r="36" ht="51" customHeight="1">
+    <row r="36" ht="51" customHeight="1" s="13">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41232,7 +41071,7 @@
         <v>730793.024</v>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="36" customHeight="1" s="13">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41295,7 +41134,7 @@
         <v>641456.819</v>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="36" customHeight="1" s="13">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41352,7 +41191,7 @@
         <v>546075.036</v>
       </c>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" ht="36" customHeight="1" s="13">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41415,7 +41254,7 @@
         <v>535524.236</v>
       </c>
     </row>
-    <row r="40" ht="36" customHeight="1">
+    <row r="40" ht="36" customHeight="1" s="13">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41478,7 +41317,7 @@
         <v>513134.296</v>
       </c>
     </row>
-    <row r="41" ht="36" customHeight="1">
+    <row r="41" ht="36" customHeight="1" s="13">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41541,7 +41380,7 @@
         <v>418738.451</v>
       </c>
     </row>
-    <row r="42" ht="36" customHeight="1">
+    <row r="42" ht="36" customHeight="1" s="13">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41604,7 +41443,7 @@
         <v>409348.485</v>
       </c>
     </row>
-    <row r="43" ht="51" customHeight="1">
+    <row r="43" ht="51" customHeight="1" s="13">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41667,7 +41506,7 @@
         <v>391148.826</v>
       </c>
     </row>
-    <row r="44" ht="36" customHeight="1">
+    <row r="44" ht="36" customHeight="1" s="13">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41730,7 +41569,7 @@
         <v>383636.504</v>
       </c>
     </row>
-    <row r="45" ht="51" customHeight="1">
+    <row r="45" ht="51" customHeight="1" s="13">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41787,7 +41626,7 @@
         <v>375866.584</v>
       </c>
     </row>
-    <row r="46" ht="66" customHeight="1">
+    <row r="46" ht="66" customHeight="1" s="13">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41844,7 +41683,7 @@
         <v>340195.148</v>
       </c>
     </row>
-    <row r="47" ht="36" customHeight="1">
+    <row r="47" ht="36" customHeight="1" s="13">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41907,7 +41746,7 @@
         <v>238734.624</v>
       </c>
     </row>
-    <row r="48" ht="51" customHeight="1">
+    <row r="48" ht="51" customHeight="1" s="13">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -41970,7 +41809,7 @@
         <v>237687.743</v>
       </c>
     </row>
-    <row r="49" ht="36" customHeight="1">
+    <row r="49" ht="36" customHeight="1" s="13">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42033,7 +41872,7 @@
         <v>232812.554</v>
       </c>
     </row>
-    <row r="50" ht="36" customHeight="1">
+    <row r="50" ht="36" customHeight="1" s="13">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42096,7 +41935,7 @@
         <v>231062.901</v>
       </c>
     </row>
-    <row r="51" ht="51" customHeight="1">
+    <row r="51" ht="51" customHeight="1" s="13">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42159,7 +41998,7 @@
         <v>222419.043</v>
       </c>
     </row>
-    <row r="52" ht="36" customHeight="1">
+    <row r="52" ht="36" customHeight="1" s="13">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42222,7 +42061,7 @@
         <v>222110.863</v>
       </c>
     </row>
-    <row r="53" ht="36" customHeight="1">
+    <row r="53" ht="36" customHeight="1" s="13">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42285,7 +42124,7 @@
         <v>217485.93</v>
       </c>
     </row>
-    <row r="54" ht="51" customHeight="1">
+    <row r="54" ht="51" customHeight="1" s="13">
       <c r="A54" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42348,7 +42187,7 @@
         <v>204057.395</v>
       </c>
     </row>
-    <row r="55" ht="51" customHeight="1">
+    <row r="55" ht="51" customHeight="1" s="13">
       <c r="A55" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42405,7 +42244,7 @@
         <v>195817.051</v>
       </c>
     </row>
-    <row r="56" ht="36" customHeight="1">
+    <row r="56" ht="36" customHeight="1" s="13">
       <c r="A56" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42468,7 +42307,7 @@
         <v>191958.178</v>
       </c>
     </row>
-    <row r="57" ht="36" customHeight="1">
+    <row r="57" ht="36" customHeight="1" s="13">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42531,7 +42370,7 @@
         <v>178082.576</v>
       </c>
     </row>
-    <row r="58" ht="36" customHeight="1">
+    <row r="58" ht="36" customHeight="1" s="13">
       <c r="A58" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42594,7 +42433,7 @@
         <v>165448.29</v>
       </c>
     </row>
-    <row r="59" ht="36" customHeight="1">
+    <row r="59" ht="36" customHeight="1" s="13">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42657,7 +42496,7 @@
         <v>165448.29</v>
       </c>
     </row>
-    <row r="60" ht="36" customHeight="1">
+    <row r="60" ht="36" customHeight="1" s="13">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42714,7 +42553,7 @@
         <v>160436.364</v>
       </c>
     </row>
-    <row r="61" ht="51" customHeight="1">
+    <row r="61" ht="51" customHeight="1" s="13">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42777,7 +42616,7 @@
         <v>146408.228</v>
       </c>
     </row>
-    <row r="62" ht="36" customHeight="1">
+    <row r="62" ht="36" customHeight="1" s="13">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42840,7 +42679,7 @@
         <v>145261.179</v>
       </c>
     </row>
-    <row r="63" ht="36" customHeight="1">
+    <row r="63" ht="36" customHeight="1" s="13">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42897,7 +42736,7 @@
         <v>115312.669</v>
       </c>
     </row>
-    <row r="64" ht="36" customHeight="1">
+    <row r="64" ht="36" customHeight="1" s="13">
       <c r="A64" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -42954,7 +42793,7 @@
         <v>113522.544</v>
       </c>
     </row>
-    <row r="65" ht="36" customHeight="1">
+    <row r="65" ht="36" customHeight="1" s="13">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43017,7 +42856,7 @@
         <v>97536.08900000001</v>
       </c>
     </row>
-    <row r="66" ht="51" customHeight="1">
+    <row r="66" ht="51" customHeight="1" s="13">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43080,7 +42919,7 @@
         <v>94820.673</v>
       </c>
     </row>
-    <row r="67" ht="36" customHeight="1">
+    <row r="67" ht="36" customHeight="1" s="13">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43137,7 +42976,7 @@
         <v>87092.753</v>
       </c>
     </row>
-    <row r="68" ht="36" customHeight="1">
+    <row r="68" ht="36" customHeight="1" s="13">
       <c r="A68" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43194,7 +43033,7 @@
         <v>85819.28200000001</v>
       </c>
     </row>
-    <row r="69" ht="36" customHeight="1">
+    <row r="69" ht="36" customHeight="1" s="13">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43251,7 +43090,7 @@
         <v>84064.859</v>
       </c>
     </row>
-    <row r="70" ht="36" customHeight="1">
+    <row r="70" ht="36" customHeight="1" s="13">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43308,7 +43147,7 @@
         <v>81111.298</v>
       </c>
     </row>
-    <row r="71" ht="51" customHeight="1">
+    <row r="71" ht="51" customHeight="1" s="13">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43371,7 +43210,7 @@
         <v>78933.788</v>
       </c>
     </row>
-    <row r="72" ht="36" customHeight="1">
+    <row r="72" ht="36" customHeight="1" s="13">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43434,7 +43273,7 @@
         <v>73299.914</v>
       </c>
     </row>
-    <row r="73" ht="51" customHeight="1">
+    <row r="73" ht="51" customHeight="1" s="13">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43491,7 +43330,7 @@
         <v>70112.436</v>
       </c>
     </row>
-    <row r="74" ht="36" customHeight="1">
+    <row r="74" ht="36" customHeight="1" s="13">
       <c r="A74" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43554,7 +43393,7 @@
         <v>68504.94899999999</v>
       </c>
     </row>
-    <row r="75" ht="36" customHeight="1">
+    <row r="75" ht="36" customHeight="1" s="13">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43611,7 +43450,7 @@
         <v>67590.72199999999</v>
       </c>
     </row>
-    <row r="76" ht="36" customHeight="1">
+    <row r="76" ht="36" customHeight="1" s="13">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43674,7 +43513,7 @@
         <v>61014.086</v>
       </c>
     </row>
-    <row r="77" ht="36" customHeight="1">
+    <row r="77" ht="36" customHeight="1" s="13">
       <c r="A77" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43737,7 +43576,7 @@
         <v>54063.278</v>
       </c>
     </row>
-    <row r="78" ht="36" customHeight="1">
+    <row r="78" ht="36" customHeight="1" s="13">
       <c r="A78" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43794,7 +43633,7 @@
         <v>51867.348</v>
       </c>
     </row>
-    <row r="79" ht="36" customHeight="1">
+    <row r="79" ht="36" customHeight="1" s="13">
       <c r="A79" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43851,7 +43690,7 @@
         <v>44138.992</v>
       </c>
     </row>
-    <row r="80" ht="36" customHeight="1">
+    <row r="80" ht="36" customHeight="1" s="13">
       <c r="A80" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43914,7 +43753,7 @@
         <v>43261.709</v>
       </c>
     </row>
-    <row r="81" ht="36" customHeight="1">
+    <row r="81" ht="36" customHeight="1" s="13">
       <c r="A81" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -43977,7 +43816,7 @@
         <v>38210.958</v>
       </c>
     </row>
-    <row r="82" ht="36" customHeight="1">
+    <row r="82" ht="36" customHeight="1" s="13">
       <c r="A82" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44040,7 +43879,7 @@
         <v>37945.049</v>
       </c>
     </row>
-    <row r="83" ht="36" customHeight="1">
+    <row r="83" ht="36" customHeight="1" s="13">
       <c r="A83" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44103,7 +43942,7 @@
         <v>37945.049</v>
       </c>
     </row>
-    <row r="84" ht="36" customHeight="1">
+    <row r="84" ht="36" customHeight="1" s="13">
       <c r="A84" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44166,7 +44005,7 @@
         <v>37945.049</v>
       </c>
     </row>
-    <row r="85" ht="36" customHeight="1">
+    <row r="85" ht="36" customHeight="1" s="13">
       <c r="A85" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44229,7 +44068,7 @@
         <v>36062.372</v>
       </c>
     </row>
-    <row r="86" ht="36" customHeight="1">
+    <row r="86" ht="36" customHeight="1" s="13">
       <c r="A86" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44292,7 +44131,7 @@
         <v>36062.372</v>
       </c>
     </row>
-    <row r="87" ht="36" customHeight="1">
+    <row r="87" ht="36" customHeight="1" s="13">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44355,7 +44194,7 @@
         <v>32710.65</v>
       </c>
     </row>
-    <row r="88" ht="36" customHeight="1">
+    <row r="88" ht="36" customHeight="1" s="13">
       <c r="A88" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44412,7 +44251,7 @@
         <v>29831.411</v>
       </c>
     </row>
-    <row r="89" ht="51" customHeight="1">
+    <row r="89" ht="51" customHeight="1" s="13">
       <c r="A89" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44469,7 +44308,7 @@
         <v>27777.798</v>
       </c>
     </row>
-    <row r="90" ht="51" customHeight="1">
+    <row r="90" ht="51" customHeight="1" s="13">
       <c r="A90" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44532,7 +44371,7 @@
         <v>27769.803</v>
       </c>
     </row>
-    <row r="91" ht="36" customHeight="1">
+    <row r="91" ht="36" customHeight="1" s="13">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44595,7 +44434,7 @@
         <v>26930.721</v>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1">
+    <row r="92" ht="36" customHeight="1" s="13">
       <c r="A92" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44658,7 +44497,7 @@
         <v>21986.6</v>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
+    <row r="93" ht="36" customHeight="1" s="13">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44715,7 +44554,7 @@
         <v>21764.075</v>
       </c>
     </row>
-    <row r="94" ht="36" customHeight="1">
+    <row r="94" ht="36" customHeight="1" s="13">
       <c r="A94" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44772,7 +44611,7 @@
         <v>21403.087</v>
       </c>
     </row>
-    <row r="95" ht="36" customHeight="1">
+    <row r="95" ht="36" customHeight="1" s="13">
       <c r="A95" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44835,7 +44674,7 @@
         <v>21142.497</v>
       </c>
     </row>
-    <row r="96" ht="51" customHeight="1">
+    <row r="96" ht="51" customHeight="1" s="13">
       <c r="A96" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44892,7 +44731,7 @@
         <v>20766.736</v>
       </c>
     </row>
-    <row r="97" ht="51" customHeight="1">
+    <row r="97" ht="51" customHeight="1" s="13">
       <c r="A97" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -44955,7 +44794,7 @@
         <v>20332.194</v>
       </c>
     </row>
-    <row r="98" ht="36" customHeight="1">
+    <row r="98" ht="36" customHeight="1" s="13">
       <c r="A98" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45012,7 +44851,7 @@
         <v>19289.495</v>
       </c>
     </row>
-    <row r="99" ht="36" customHeight="1">
+    <row r="99" ht="36" customHeight="1" s="13">
       <c r="A99" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45075,7 +44914,7 @@
         <v>17042.087</v>
       </c>
     </row>
-    <row r="100" ht="36" customHeight="1">
+    <row r="100" ht="36" customHeight="1" s="13">
       <c r="A100" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45138,7 +44977,7 @@
         <v>15485.573</v>
       </c>
     </row>
-    <row r="101" ht="36" customHeight="1">
+    <row r="101" ht="36" customHeight="1" s="13">
       <c r="A101" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45201,7 +45040,7 @@
         <v>15485.573</v>
       </c>
     </row>
-    <row r="102" ht="36" customHeight="1">
+    <row r="102" ht="36" customHeight="1" s="13">
       <c r="A102" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45264,7 +45103,7 @@
         <v>15375.262</v>
       </c>
     </row>
-    <row r="103" ht="51" customHeight="1">
+    <row r="103" ht="51" customHeight="1" s="13">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45321,7 +45160,7 @@
         <v>15329.051</v>
       </c>
     </row>
-    <row r="104" ht="36" customHeight="1">
+    <row r="104" ht="36" customHeight="1" s="13">
       <c r="A104" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45378,7 +45217,7 @@
         <v>14163.266</v>
       </c>
     </row>
-    <row r="105" ht="36" customHeight="1">
+    <row r="105" ht="36" customHeight="1" s="13">
       <c r="A105" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45441,7 +45280,7 @@
         <v>10728.234</v>
       </c>
     </row>
-    <row r="106" ht="36" customHeight="1">
+    <row r="106" ht="36" customHeight="1" s="13">
       <c r="A106" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45504,7 +45343,7 @@
         <v>10608.624</v>
       </c>
     </row>
-    <row r="107" ht="51" customHeight="1">
+    <row r="107" ht="51" customHeight="1" s="13">
       <c r="A107" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45567,7 +45406,7 @@
         <v>10295.909</v>
       </c>
     </row>
-    <row r="108" ht="36" customHeight="1">
+    <row r="108" ht="36" customHeight="1" s="13">
       <c r="A108" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45630,7 +45469,7 @@
         <v>9517.895</v>
       </c>
     </row>
-    <row r="109" ht="36" customHeight="1">
+    <row r="109" ht="36" customHeight="1" s="13">
       <c r="A109" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45693,7 +45532,7 @@
         <v>9106.644</v>
       </c>
     </row>
-    <row r="110" ht="36" customHeight="1">
+    <row r="110" ht="36" customHeight="1" s="13">
       <c r="A110" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45756,7 +45595,7 @@
         <v>7636.511</v>
       </c>
     </row>
-    <row r="111" ht="36" customHeight="1">
+    <row r="111" ht="36" customHeight="1" s="13">
       <c r="A111" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45813,7 +45652,7 @@
         <v>7581.252</v>
       </c>
     </row>
-    <row r="112" ht="36" customHeight="1">
+    <row r="112" ht="36" customHeight="1" s="13">
       <c r="A112" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45870,7 +45709,7 @@
         <v>7260.354</v>
       </c>
     </row>
-    <row r="113" ht="51" customHeight="1">
+    <row r="113" ht="51" customHeight="1" s="13">
       <c r="A113" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45933,7 +45772,7 @@
         <v>6619.166</v>
       </c>
     </row>
-    <row r="114" ht="51" customHeight="1">
+    <row r="114" ht="51" customHeight="1" s="13">
       <c r="A114" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -45996,7 +45835,7 @@
         <v>5637.236</v>
       </c>
     </row>
-    <row r="115" ht="36" customHeight="1">
+    <row r="115" ht="36" customHeight="1" s="13">
       <c r="A115" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46059,7 +45898,7 @@
         <v>5635.112</v>
       </c>
     </row>
-    <row r="116" ht="36" customHeight="1">
+    <row r="116" ht="36" customHeight="1" s="13">
       <c r="A116" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46122,7 +45961,7 @@
         <v>5635.112</v>
       </c>
     </row>
-    <row r="117" ht="36" customHeight="1">
+    <row r="117" ht="36" customHeight="1" s="13">
       <c r="A117" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46185,7 +46024,7 @@
         <v>5635.112</v>
       </c>
     </row>
-    <row r="118" ht="36" customHeight="1">
+    <row r="118" ht="36" customHeight="1" s="13">
       <c r="A118" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46248,7 +46087,7 @@
         <v>5635.112</v>
       </c>
     </row>
-    <row r="119" ht="51" customHeight="1">
+    <row r="119" ht="51" customHeight="1" s="13">
       <c r="A119" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46311,7 +46150,7 @@
         <v>3135.817</v>
       </c>
     </row>
-    <row r="120" ht="36" customHeight="1">
+    <row r="120" ht="36" customHeight="1" s="13">
       <c r="A120" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46374,7 +46213,7 @@
         <v>2973.471</v>
       </c>
     </row>
-    <row r="121" ht="36" customHeight="1">
+    <row r="121" ht="36" customHeight="1" s="13">
       <c r="A121" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46437,7 +46276,7 @@
         <v>2973.471</v>
       </c>
     </row>
-    <row r="122" ht="36" customHeight="1">
+    <row r="122" ht="36" customHeight="1" s="13">
       <c r="A122" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46500,7 +46339,7 @@
         <v>2973.471</v>
       </c>
     </row>
-    <row r="123" ht="36" customHeight="1">
+    <row r="123" ht="36" customHeight="1" s="13">
       <c r="A123" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46563,7 +46402,7 @@
         <v>2973.471</v>
       </c>
     </row>
-    <row r="124" ht="36" customHeight="1">
+    <row r="124" ht="36" customHeight="1" s="13">
       <c r="A124" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46626,7 +46465,7 @@
         <v>2838.35</v>
       </c>
     </row>
-    <row r="125" ht="36" customHeight="1">
+    <row r="125" ht="36" customHeight="1" s="13">
       <c r="A125" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46689,7 +46528,7 @@
         <v>2838.35</v>
       </c>
     </row>
-    <row r="126" ht="36" customHeight="1">
+    <row r="126" ht="36" customHeight="1" s="13">
       <c r="A126" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46752,7 +46591,7 @@
         <v>2478.101</v>
       </c>
     </row>
-    <row r="127" ht="51" customHeight="1">
+    <row r="127" ht="51" customHeight="1" s="13">
       <c r="A127" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46815,7 +46654,7 @@
         <v>2356.585</v>
       </c>
     </row>
-    <row r="128" ht="36" customHeight="1">
+    <row r="128" ht="36" customHeight="1" s="13">
       <c r="A128" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46878,7 +46717,7 @@
         <v>2182.088</v>
       </c>
     </row>
-    <row r="129" ht="36" customHeight="1">
+    <row r="129" ht="36" customHeight="1" s="13">
       <c r="A129" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46935,7 +46774,7 @@
         <v>2037.747</v>
       </c>
     </row>
-    <row r="130" ht="36" customHeight="1">
+    <row r="130" ht="36" customHeight="1" s="13">
       <c r="A130" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -46992,7 +46831,7 @@
         <v>2017.182</v>
       </c>
     </row>
-    <row r="131" ht="36" customHeight="1">
+    <row r="131" ht="36" customHeight="1" s="13">
       <c r="A131" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47049,7 +46888,7 @@
         <v>1936.137</v>
       </c>
     </row>
-    <row r="132" ht="51" customHeight="1">
+    <row r="132" ht="51" customHeight="1" s="13">
       <c r="A132" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47106,7 +46945,7 @@
         <v>1596.923</v>
       </c>
     </row>
-    <row r="133" ht="36" customHeight="1">
+    <row r="133" ht="36" customHeight="1" s="13">
       <c r="A133" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47169,7 +47008,7 @@
         <v>1468.252</v>
       </c>
     </row>
-    <row r="134" ht="36" customHeight="1">
+    <row r="134" ht="36" customHeight="1" s="13">
       <c r="A134" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47232,7 +47071,7 @@
         <v>1370.09</v>
       </c>
     </row>
-    <row r="135" ht="36" customHeight="1">
+    <row r="135" ht="36" customHeight="1" s="13">
       <c r="A135" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47289,7 +47128,7 @@
         <v>1185.585</v>
       </c>
     </row>
-    <row r="136" ht="51" customHeight="1">
+    <row r="136" ht="51" customHeight="1" s="13">
       <c r="A136" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47352,7 +47191,7 @@
         <v>1141.535</v>
       </c>
     </row>
-    <row r="137" ht="51" customHeight="1">
+    <row r="137" ht="51" customHeight="1" s="13">
       <c r="A137" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47415,7 +47254,7 @@
         <v>964.047</v>
       </c>
     </row>
-    <row r="138" ht="36" customHeight="1">
+    <row r="138" ht="36" customHeight="1" s="13">
       <c r="A138" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47472,7 +47311,7 @@
         <v>743.317</v>
       </c>
     </row>
-    <row r="139" ht="36" customHeight="1">
+    <row r="139" ht="36" customHeight="1" s="13">
       <c r="A139" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47529,7 +47368,7 @@
         <v>565.899</v>
       </c>
     </row>
-    <row r="140" ht="51" customHeight="1">
+    <row r="140" ht="51" customHeight="1" s="13">
       <c r="A140" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47592,7 +47431,7 @@
         <v>531.083</v>
       </c>
     </row>
-    <row r="141" ht="51" customHeight="1">
+    <row r="141" ht="51" customHeight="1" s="13">
       <c r="A141" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47655,7 +47494,7 @@
         <v>517.999</v>
       </c>
     </row>
-    <row r="142" ht="36" customHeight="1">
+    <row r="142" ht="36" customHeight="1" s="13">
       <c r="A142" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47712,7 +47551,7 @@
         <v>488.429</v>
       </c>
     </row>
-    <row r="143" ht="36" customHeight="1">
+    <row r="143" ht="36" customHeight="1" s="13">
       <c r="A143" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47769,7 +47608,7 @@
         <v>463.476</v>
       </c>
     </row>
-    <row r="144" ht="36" customHeight="1">
+    <row r="144" ht="36" customHeight="1" s="13">
       <c r="A144" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47832,7 +47671,7 @@
         <v>383.615</v>
       </c>
     </row>
-    <row r="145" ht="51" customHeight="1">
+    <row r="145" ht="51" customHeight="1" s="13">
       <c r="A145" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47895,7 +47734,7 @@
         <v>282.206</v>
       </c>
     </row>
-    <row r="146" ht="36" customHeight="1">
+    <row r="146" ht="36" customHeight="1" s="13">
       <c r="A146" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -47958,7 +47797,7 @@
         <v>254.077</v>
       </c>
     </row>
-    <row r="147" ht="36" customHeight="1">
+    <row r="147" ht="36" customHeight="1" s="13">
       <c r="A147" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48021,7 +47860,7 @@
         <v>238.86</v>
       </c>
     </row>
-    <row r="148" ht="36" customHeight="1">
+    <row r="148" ht="36" customHeight="1" s="13">
       <c r="A148" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48084,7 +47923,7 @@
         <v>203.576</v>
       </c>
     </row>
-    <row r="149" ht="36" customHeight="1">
+    <row r="149" ht="36" customHeight="1" s="13">
       <c r="A149" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48147,7 +47986,7 @@
         <v>150.563</v>
       </c>
     </row>
-    <row r="150" ht="36" customHeight="1">
+    <row r="150" ht="36" customHeight="1" s="13">
       <c r="A150" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48204,7 +48043,7 @@
         <v>115.673</v>
       </c>
     </row>
-    <row r="151" ht="36" customHeight="1">
+    <row r="151" ht="36" customHeight="1" s="13">
       <c r="A151" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48267,7 +48106,7 @@
         <v>111.992</v>
       </c>
     </row>
-    <row r="152" ht="36" customHeight="1">
+    <row r="152" ht="36" customHeight="1" s="13">
       <c r="A152" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48330,7 +48169,7 @@
         <v>78.602</v>
       </c>
     </row>
-    <row r="153" ht="36" customHeight="1">
+    <row r="153" ht="36" customHeight="1" s="13">
       <c r="A153" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48387,7 +48226,7 @@
         <v>33.928</v>
       </c>
     </row>
-    <row r="154" ht="51" customHeight="1">
+    <row r="154" ht="51" customHeight="1" s="13">
       <c r="A154" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48450,7 +48289,7 @@
         <v>25.65</v>
       </c>
     </row>
-    <row r="155" ht="36" customHeight="1">
+    <row r="155" ht="36" customHeight="1" s="13">
       <c r="A155" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48507,7 +48346,7 @@
         <v>7.067</v>
       </c>
     </row>
-    <row r="156" ht="36" customHeight="1">
+    <row r="156" ht="36" customHeight="1" s="13">
       <c r="A156" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48564,7 +48403,7 @@
         <v>6.812</v>
       </c>
     </row>
-    <row r="157" ht="36" customHeight="1">
+    <row r="157" ht="36" customHeight="1" s="13">
       <c r="A157" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48621,7 +48460,7 @@
         <v>5.272</v>
       </c>
     </row>
-    <row r="158" ht="36" customHeight="1">
+    <row r="158" ht="36" customHeight="1" s="13">
       <c r="A158" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48684,7 +48523,7 @@
         <v>4.606</v>
       </c>
     </row>
-    <row r="159" ht="36" customHeight="1">
+    <row r="159" ht="36" customHeight="1" s="13">
       <c r="A159" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48741,7 +48580,7 @@
         <v>2.341</v>
       </c>
     </row>
-    <row r="160" ht="51" customHeight="1">
+    <row r="160" ht="51" customHeight="1" s="13">
       <c r="A160" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48798,7 +48637,7 @@
         <v>1.999</v>
       </c>
     </row>
-    <row r="161" ht="51" customHeight="1">
+    <row r="161" ht="51" customHeight="1" s="13">
       <c r="A161" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48861,7 +48700,7 @@
         <v>1.196</v>
       </c>
     </row>
-    <row r="162" ht="36" customHeight="1">
+    <row r="162" ht="36" customHeight="1" s="13">
       <c r="A162" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48918,7 +48757,7 @@
         <v>1.059</v>
       </c>
     </row>
-    <row r="163" ht="36" customHeight="1">
+    <row r="163" ht="36" customHeight="1" s="13">
       <c r="A163" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -48975,7 +48814,7 @@
         <v>1.048</v>
       </c>
     </row>
-    <row r="164" ht="36" customHeight="1">
+    <row r="164" ht="36" customHeight="1" s="13">
       <c r="A164" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49032,7 +48871,7 @@
         <v>0.959</v>
       </c>
     </row>
-    <row r="165" ht="51" customHeight="1">
+    <row r="165" ht="51" customHeight="1" s="13">
       <c r="A165" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49095,7 +48934,7 @@
         <v>0.092</v>
       </c>
     </row>
-    <row r="166" ht="36" customHeight="1">
+    <row r="166" ht="36" customHeight="1" s="13">
       <c r="A166" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49152,7 +48991,7 @@
         <v>0.038</v>
       </c>
     </row>
-    <row r="167" ht="36" customHeight="1">
+    <row r="167" ht="36" customHeight="1" s="13">
       <c r="A167" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49215,7 +49054,7 @@
         <v>0.014</v>
       </c>
     </row>
-    <row r="168" ht="36" customHeight="1">
+    <row r="168" ht="36" customHeight="1" s="13">
       <c r="A168" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49272,7 +49111,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="169" ht="36" customHeight="1">
+    <row r="169" ht="36" customHeight="1" s="13">
       <c r="A169" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49329,7 +49168,7 @@
         <v>0.007</v>
       </c>
     </row>
-    <row r="170" ht="36" customHeight="1">
+    <row r="170" ht="36" customHeight="1" s="13">
       <c r="A170" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49386,7 +49225,7 @@
         <v>0.005</v>
       </c>
     </row>
-    <row r="171" ht="51" customHeight="1">
+    <row r="171" ht="51" customHeight="1" s="13">
       <c r="A171" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49449,7 +49288,7 @@
         <v>0.001</v>
       </c>
     </row>
-    <row r="172" ht="36" customHeight="1">
+    <row r="172" ht="36" customHeight="1" s="13">
       <c r="A172" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49506,7 +49345,7 @@
         <v>0.001</v>
       </c>
     </row>
-    <row r="173" ht="36" customHeight="1">
+    <row r="173" ht="36" customHeight="1" s="13">
       <c r="A173" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49563,7 +49402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" ht="36" customHeight="1">
+    <row r="174" ht="36" customHeight="1" s="13">
       <c r="A174" s="5" t="inlineStr">
         <is>
           <t>LME_052</t>
@@ -49635,9 +49474,9 @@
   <dimension ref="A1:C140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" style="13" min="1" max="1"/>
+    <col width="22" customWidth="1" style="13" min="2" max="2"/>
+    <col width="14" customWidth="1" style="13" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49649,6 +49488,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -51376,6 +51216,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -51415,31 +51256,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="46" customWidth="1" style="13" min="1" max="1"/>
+    <col width="32" customWidth="1" style="13" min="2" max="2"/>
+    <col width="20" customWidth="1" style="13" min="3" max="3"/>
+    <col width="20" customWidth="1" style="13" min="4" max="4"/>
+    <col width="20" customWidth="1" style="13" min="5" max="5"/>
+    <col width="20" customWidth="1" style="13" min="6" max="6"/>
+    <col width="20" customWidth="1" style="13" min="7" max="7"/>
+    <col width="20" customWidth="1" style="13" min="8" max="8"/>
+    <col width="20" customWidth="1" style="13" min="9" max="9"/>
+    <col width="20" customWidth="1" style="13" min="10" max="10"/>
+    <col width="20" customWidth="1" style="13" min="11" max="11"/>
+    <col width="20" customWidth="1" style="13" min="12" max="12"/>
+    <col width="20" customWidth="1" style="13" min="13" max="13"/>
+    <col width="20" customWidth="1" style="13" min="14" max="14"/>
+    <col width="20" customWidth="1" style="13" min="15" max="15"/>
+    <col width="20" customWidth="1" style="13" min="16" max="16"/>
+    <col width="20" customWidth="1" style="13" min="17" max="17"/>
+    <col width="20" customWidth="1" style="13" min="18" max="18"/>
+    <col width="20" customWidth="1" style="13" min="19" max="19"/>
+    <col width="20" customWidth="1" style="13" min="20" max="20"/>
+    <col width="20" customWidth="1" style="13" min="21" max="21"/>
+    <col width="20" customWidth="1" style="13" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -51449,14 +51290,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="13">
+      <c r="A2" t="inlineStr">
         <is>
           <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="13">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>model</t>
@@ -51565,6 +51407,16 @@
       <c r="V4" s="14" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -51630,6 +51482,12 @@
       <c r="V5" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -51702,6 +51560,12 @@
       <c r="V6" s="15" t="n">
         <v>0.9515593841782986</v>
       </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -51774,6 +51638,12 @@
       <c r="V7" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -51846,6 +51716,12 @@
       <c r="V8" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -51865,10 +51741,10 @@
         <v>10</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>4.577821514309684</v>
@@ -51917,6 +51793,12 @@
       </c>
       <c r="V9" s="15" t="n">
         <v>4.505329171349933</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="10">
@@ -51937,10 +51819,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>23.08353417746487</v>
+        <v>17.5405588673282</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>15.90255241749527</v>
@@ -51989,6 +51871,12 @@
       </c>
       <c r="V10" s="15" t="n">
         <v>59.77915649033152</v>
+      </c>
+      <c r="W10" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X10" t="n">
+        <v>18.26147259967061</v>
       </c>
     </row>
     <row r="11">
@@ -52009,10 +51897,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>5.280025044025574</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>4.253960143076137</v>
@@ -52061,6 +51949,12 @@
       </c>
       <c r="V11" s="15" t="n">
         <v>4.076903184343629</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="12">
@@ -52081,10 +51975,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>27.87866446553727</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>35.33173047665775</v>
@@ -52133,6 +52027,12 @@
       </c>
       <c r="V12" s="15" t="n">
         <v>35.71211791968918</v>
+      </c>
+      <c r="W12" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22.05491859863601</v>
       </c>
     </row>
     <row r="13">
@@ -52153,10 +52053,10 @@
         <v>192.1678373016385</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>44.69612244609182</v>
+        <v>32.66594692768881</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>82.34673248644883</v>
+        <v>52.72727295358897</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>2095.248025656152</v>
@@ -52205,6 +52105,12 @@
       </c>
       <c r="V13" s="15" t="n">
         <v>14877.93741284232</v>
+      </c>
+      <c r="W13" t="n">
+        <v>34.20335794997818</v>
+      </c>
+      <c r="X13" t="n">
+        <v>56.22377819574023</v>
       </c>
     </row>
     <row r="14">
@@ -52225,10 +52131,10 @@
         <v>957.3100822228713</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>142.6316473278907</v>
+        <v>94.72342790053084</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>119.6790259721415</v>
+        <v>79.26175744474504</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>66.85909344832929</v>
@@ -52277,6 +52183,12 @@
       </c>
       <c r="V14" s="15" t="n">
         <v>273.2189846219271</v>
+      </c>
+      <c r="W14" t="n">
+        <v>100.5843105009133</v>
+      </c>
+      <c r="X14" t="n">
+        <v>84.19886949576215</v>
       </c>
     </row>
     <row r="15">
@@ -52297,10 +52209,10 @@
         <v>95.89664212630589</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>27.04720839963061</v>
+        <v>20.6038616514508</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>56.07159249521006</v>
+        <v>37.70118799536801</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>87.69028664784985</v>
@@ -52349,6 +52261,12 @@
       </c>
       <c r="V15" s="15" t="n">
         <v>203.4330067474349</v>
+      </c>
+      <c r="W15" t="n">
+        <v>21.44281722434658</v>
+      </c>
+      <c r="X15" t="n">
+        <v>39.93433564550757</v>
       </c>
     </row>
     <row r="16">
@@ -52369,10 +52287,10 @@
         <v>803.5261221856176</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>125.6774988481667</v>
+        <v>84.34008081145512</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>112.9513560225056</v>
+        <v>75.07568037774374</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>125.8278976901746</v>
@@ -52421,6 +52339,12 @@
       </c>
       <c r="V16" s="15" t="n">
         <v>471.8097034434562</v>
+      </c>
+      <c r="W16" t="n">
+        <v>89.42144416594054</v>
+      </c>
+      <c r="X16" t="n">
+        <v>79.70868801149217</v>
       </c>
     </row>
     <row r="17">
@@ -52441,10 +52365,10 @@
         <v>433.072663830632</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>80.40326471437805</v>
+        <v>55.98311339669585</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>90.8347559055665</v>
+        <v>60.95093876890394</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>595.980810547916</v>
@@ -52493,6 +52417,12 @@
       </c>
       <c r="V17" s="15" t="n">
         <v>1722.34384103534</v>
+      </c>
+      <c r="W17" t="n">
+        <v>59.0359960319099</v>
+      </c>
+      <c r="X17" t="n">
+        <v>64.61365241945592</v>
       </c>
     </row>
     <row r="18">
@@ -52513,10 +52443,10 @@
         <v>148.9361077710915</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>37.17816837124528</v>
+        <v>27.58755563311879</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>44.67286555238029</v>
+        <v>31.8383297901462</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>62.99526927008372</v>
@@ -52565,6 +52495,12 @@
       </c>
       <c r="V18" s="15" t="n">
         <v>121.8463895038143</v>
+      </c>
+      <c r="W18" t="n">
+        <v>28.82163947920901</v>
+      </c>
+      <c r="X18" t="n">
+        <v>33.45014159768149</v>
       </c>
     </row>
     <row r="19">
@@ -52585,10 +52521,10 @@
         <v>100.4615790278394</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>27.97159534955067</v>
+        <v>21.24902966393597</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>31.85962489709726</v>
+        <v>23.64253547366279</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>94.46318860159323</v>
@@ -52637,6 +52573,12 @@
       </c>
       <c r="V19" s="15" t="n">
         <v>94.42462805535909</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.12325191669997</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24.69537328805766</v>
       </c>
     </row>
     <row r="20">
@@ -52657,10 +52599,10 @@
         <v>458.5494665163353</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>83.79409714898284</v>
+        <v>58.14554747625077</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>218.4235569116157</v>
+        <v>128.9663065620963</v>
       </c>
       <c r="G20" s="15" t="n">
         <v>526.4921571234207</v>
@@ -52709,6 +52651,12 @@
       </c>
       <c r="V20" s="15" t="n">
         <v>6233.035289922082</v>
+      </c>
+      <c r="W20" t="n">
+        <v>61.34701549533092</v>
+      </c>
+      <c r="X20" t="n">
+        <v>139.2690881142819</v>
       </c>
     </row>
     <row r="21">
@@ -52729,10 +52677,10 @@
         <v>1149.569644128419</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>162.7994465457392</v>
+        <v>106.9436311896749</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>419.1319331031422</v>
+        <v>227.6776140763192</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>2742.0026218271</v>
@@ -52781,6 +52729,12 @@
       </c>
       <c r="V21" s="15" t="n">
         <v>1095224.597367184</v>
+      </c>
+      <c r="W21" t="n">
+        <v>113.7425428506414</v>
+      </c>
+      <c r="X21" t="n">
+        <v>248.6773298608114</v>
       </c>
     </row>
     <row r="22">
@@ -52801,10 +52755,10 @@
         <v>233.2433400524923</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>51.41196048219524</v>
+        <v>37.14266240597716</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>126.5194176558155</v>
+        <v>75.84076780880021</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>324.1174761836669</v>
@@ -52853,6 +52807,12 @@
       </c>
       <c r="V22" s="15" t="n">
         <v>2786.139764177064</v>
+      </c>
+      <c r="W22" t="n">
+        <v>38.95671499956013</v>
+      </c>
+      <c r="X22" t="n">
+        <v>81.61491907909036</v>
       </c>
     </row>
     <row r="23">
@@ -52873,10 +52833,10 @@
         <v>707.6563663686329</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>114.6526832161108</v>
+        <v>77.52663157506882</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>277.5429147385729</v>
+        <v>159.3851682131666</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>7317.526805497487</v>
@@ -52925,6 +52885,12 @@
       </c>
       <c r="V23" s="15" t="n">
         <v>1645094.341484428</v>
+      </c>
+      <c r="W23" t="n">
+        <v>82.1062067044645</v>
+      </c>
+      <c r="X23" t="n">
+        <v>172.7159821560637</v>
       </c>
     </row>
     <row r="24">
@@ -52945,10 +52911,10 @@
         <v>14.25607593602188</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>6.822160362509687</v>
+        <v>5.822500744826133</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>9.974089204406337</v>
+        <v>7.886641531625287</v>
       </c>
       <c r="G24" s="15" t="n">
         <v>16.07734930921978</v>
@@ -52997,6 +52963,12 @@
       </c>
       <c r="V24" s="15" t="n">
         <v>23.7201163809729</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5.959401555272611</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.157400780495703</v>
       </c>
     </row>
     <row r="25">
@@ -53017,10 +52989,10 @@
         <v>260.6153549998892</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>55.70427595599621</v>
+        <v>39.97825302781153</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>66.98390168951386</v>
+        <v>45.95644332462776</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>104.2460481282354</v>
@@ -53069,6 +53041,12 @@
       </c>
       <c r="V25" s="15" t="n">
         <v>310.1782655945706</v>
+      </c>
+      <c r="W25" t="n">
+        <v>41.97151006807996</v>
+      </c>
+      <c r="X25" t="n">
+        <v>48.55654078178316</v>
       </c>
     </row>
     <row r="26">
@@ -53089,10 +53067,10 @@
         <v>537.7936739979261</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>94.02452572065314</v>
+        <v>64.62730910556859</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>104.5984655435359</v>
+        <v>68.89654834470186</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>157.1760602802228</v>
@@ -53141,6 +53119,12 @@
       </c>
       <c r="V26" s="15" t="n">
         <v>768.3150282244065</v>
+      </c>
+      <c r="W26" t="n">
+        <v>68.28079088333945</v>
+      </c>
+      <c r="X26" t="n">
+        <v>73.22489200527703</v>
       </c>
     </row>
     <row r="27">
@@ -53161,10 +53145,10 @@
         <v>614.0613855691029</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>103.4813688456822</v>
+        <v>70.56716399283415</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>102.7621261364643</v>
+        <v>68.60061415059394</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>206.6330656441522</v>
@@ -53213,6 +53197,12 @@
       </c>
       <c r="V27" s="15" t="n">
         <v>748.5026573846656</v>
+      </c>
+      <c r="W27" t="n">
+        <v>74.64296450565553</v>
+      </c>
+      <c r="X27" t="n">
+        <v>72.78499931797944</v>
       </c>
     </row>
     <row r="28">
@@ -53233,10 +53223,10 @@
         <v>472.1088760681196</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>85.5773999698382</v>
+        <v>59.279899273387</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>143.4905091038848</v>
+        <v>90.11143273373939</v>
       </c>
       <c r="G28" s="15" t="n">
         <v>948.2646461013878</v>
@@ -53285,6 +53275,12 @@
       </c>
       <c r="V28" s="15" t="n">
         <v>2766.021116765205</v>
+      </c>
+      <c r="W28" t="n">
+        <v>62.55976718436576</v>
+      </c>
+      <c r="X28" t="n">
+        <v>96.42460617606433</v>
       </c>
     </row>
     <row r="29">
@@ -53305,10 +53301,10 @@
         <v>443.19575516822</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>81.75704873945472</v>
+        <v>56.84734670066118</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>137.4895374643425</v>
+        <v>86.18089558214803</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>811.720324648783</v>
@@ -53357,6 +53353,12 @@
       </c>
       <c r="V29" s="15" t="n">
         <v>2351.352010120519</v>
+      </c>
+      <c r="W29" t="n">
+        <v>59.95947384551975</v>
+      </c>
+      <c r="X29" t="n">
+        <v>92.23948616526582</v>
       </c>
     </row>
     <row r="30">
@@ -53377,10 +53379,10 @@
         <v>3690.679934159451</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>378.1981726321904</v>
+        <v>231.747404317973</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>592.0104834453182</v>
+        <v>330.6351772171339</v>
       </c>
       <c r="G30" s="15" t="n">
         <v>0</v>
@@ -53429,6 +53431,12 @@
       </c>
       <c r="V30" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>249.0080859298023</v>
+      </c>
+      <c r="X30" t="n">
+        <v>359.9372982916983</v>
       </c>
     </row>
     <row r="31">
@@ -53449,10 +53457,10 @@
         <v>6316.900158152956</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>557.6747112644658</v>
+        <v>330.9474462171082</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>600.4669169174184</v>
+        <v>342.8897408224037</v>
       </c>
       <c r="G31" s="15" t="n">
         <v>196639.6235546877</v>
@@ -53501,6 +53509,12 @@
       </c>
       <c r="V31" s="15" t="n">
         <v>12867258.24483938</v>
+      </c>
+      <c r="W31" t="n">
+        <v>357.2719697561159</v>
+      </c>
+      <c r="X31" t="n">
+        <v>372.1577950636552</v>
       </c>
     </row>
     <row r="32">
@@ -53521,10 +53535,10 @@
         <v>8002.573841696399</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>661.6285267329362</v>
+        <v>387.1389168651923</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>636.0407247825135</v>
+        <v>363.6412451787915</v>
       </c>
       <c r="G32" s="15" t="n">
         <v>0</v>
@@ -53573,6 +53587,12 @@
       </c>
       <c r="V32" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>418.7985782328224</v>
+      </c>
+      <c r="X32" t="n">
+        <v>394.6609619468547</v>
       </c>
     </row>
     <row r="33">
@@ -53593,10 +53613,10 @@
         <v>2832.954810656827</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>312.4011249072236</v>
+        <v>194.4721790061764</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>519.6938790691926</v>
+        <v>291.1028404040098</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>841359.9861091692</v>
@@ -53645,6 +53665,12 @@
       </c>
       <c r="V33" s="15" t="n">
         <v>1414639309.654173</v>
+      </c>
+      <c r="W33" t="n">
+        <v>208.4737632540628</v>
+      </c>
+      <c r="X33" t="n">
+        <v>316.6996488939066</v>
       </c>
     </row>
     <row r="34">
@@ -53665,10 +53691,10 @@
         <v>652.8956149848666</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>108.1701370776778</v>
+        <v>73.49534453944611</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>269.9290920813721</v>
+        <v>157.3739344485984</v>
       </c>
       <c r="G34" s="15" t="n">
         <v>158437.3698017728</v>
@@ -53717,6 +53743,12 @@
       </c>
       <c r="V34" s="15" t="n">
         <v>484185.117512574</v>
+      </c>
+      <c r="W34" t="n">
+        <v>77.7819763119403</v>
+      </c>
+      <c r="X34" t="n">
+        <v>170.2280375697981</v>
       </c>
     </row>
     <row r="35">
@@ -53781,6 +53813,12 @@
       <c r="V35" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -53853,6 +53891,12 @@
       <c r="V36" s="15" t="n">
         <v>0.8537152806236192</v>
       </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -53872,10 +53916,10 @@
         <v>416.179587813214</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>56.28900254449202</v>
+        <v>73.16902902025888</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>88.59793106865003</v>
+        <v>124.051602358648</v>
       </c>
       <c r="G37" s="15" t="n">
         <v>0</v>
@@ -53924,6 +53968,12 @@
       </c>
       <c r="V37" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>76.0908418656785</v>
+      </c>
+      <c r="X37" t="n">
+        <v>130.495353702711</v>
       </c>
     </row>
     <row r="38">
@@ -53944,10 +53994,10 @@
         <v>357.8589689857071</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>50.88677450113939</v>
+        <v>65.71390752353284</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>78.79467664999078</v>
+        <v>109.0006292271502</v>
       </c>
       <c r="G38" s="15" t="n">
         <v>1974.676817436918</v>
@@ -53996,6 +54046,12 @@
       </c>
       <c r="V38" s="15" t="n">
         <v>50303.53156474263</v>
+      </c>
+      <c r="W38" t="n">
+        <v>68.27106823443432</v>
+      </c>
+      <c r="X38" t="n">
+        <v>114.4546145406711</v>
       </c>
     </row>
     <row r="39">
@@ -54016,10 +54072,10 @@
         <v>199.0673338987186</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>34.38626616103237</v>
+        <v>43.28733232006891</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>45.45142535053177</v>
+        <v>59.41950984806437</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>403.5448329427017</v>
@@ -54068,6 +54124,12 @@
       </c>
       <c r="V39" s="15" t="n">
         <v>388.7214670416733</v>
+      </c>
+      <c r="W39" t="n">
+        <v>44.80088239744686</v>
+      </c>
+      <c r="X39" t="n">
+        <v>61.85648360648175</v>
       </c>
     </row>
     <row r="40">
@@ -54088,10 +54150,10 @@
         <v>19.90673338987186</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>7.380758154301324</v>
+        <v>8.406014400535831</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>9.755812879175473</v>
+        <v>11.53873959620375</v>
       </c>
       <c r="G40" s="15" t="n">
         <v>10.13479730321421</v>
@@ -54140,6 +54202,12 @@
       </c>
       <c r="V40" s="15" t="n">
         <v>9.515134778306953</v>
+      </c>
+      <c r="W40" t="n">
+        <v>8.570844148075091</v>
+      </c>
+      <c r="X40" t="n">
+        <v>11.83374639445339</v>
       </c>
     </row>
     <row r="41">
@@ -54160,10 +54228,10 @@
         <v>174.1521562345644</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>31.44683930314632</v>
+        <v>39.35749816288925</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>33.95247504464749</v>
+        <v>43.88701766727957</v>
       </c>
       <c r="G41" s="15" t="n">
         <v>72.37923796403966</v>
@@ -54212,6 +54280,12 @@
       </c>
       <c r="V41" s="15" t="n">
         <v>2184.01743144918</v>
+      </c>
+      <c r="W41" t="n">
+        <v>40.69829501237073</v>
+      </c>
+      <c r="X41" t="n">
+        <v>45.61090054732936</v>
       </c>
     </row>
     <row r="42">
@@ -54232,10 +54306,10 @@
         <v>98.07449751016838</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>21.42521366403237</v>
+        <v>26.1535868392652</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>17.87446335772178</v>
+        <v>21.83387403064396</v>
       </c>
       <c r="G42" s="15" t="n">
         <v>22.48481592273476</v>
@@ -54284,6 +54358,12 @@
       </c>
       <c r="V42" s="15" t="n">
         <v>377.6757630310734</v>
+      </c>
+      <c r="W42" t="n">
+        <v>26.94393320884064</v>
+      </c>
+      <c r="X42" t="n">
+        <v>22.49596958420992</v>
       </c>
     </row>
     <row r="43">
@@ -54304,10 +54384,10 @@
         <v>10</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>4.658907044799036</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>4.658907044799037</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="G43" s="15" t="n">
         <v>5.046009141842525</v>
@@ -54356,6 +54436,12 @@
       </c>
       <c r="V43" s="15" t="n">
         <v>4.830501414419818</v>
+      </c>
+      <c r="W43" t="n">
+        <v>5.2271260127287</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5.2271260127287</v>
       </c>
     </row>
     <row r="44">
@@ -54427,6 +54513,12 @@
         <v>1</v>
       </c>
       <c r="V44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -54441,31 +54533,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="46" customWidth="1" style="13" min="1" max="1"/>
+    <col width="32" customWidth="1" style="13" min="2" max="2"/>
+    <col width="20" customWidth="1" style="13" min="3" max="3"/>
+    <col width="20" customWidth="1" style="13" min="4" max="4"/>
+    <col width="20" customWidth="1" style="13" min="5" max="5"/>
+    <col width="20" customWidth="1" style="13" min="6" max="6"/>
+    <col width="20" customWidth="1" style="13" min="7" max="7"/>
+    <col width="20" customWidth="1" style="13" min="8" max="8"/>
+    <col width="20" customWidth="1" style="13" min="9" max="9"/>
+    <col width="20" customWidth="1" style="13" min="10" max="10"/>
+    <col width="20" customWidth="1" style="13" min="11" max="11"/>
+    <col width="20" customWidth="1" style="13" min="12" max="12"/>
+    <col width="20" customWidth="1" style="13" min="13" max="13"/>
+    <col width="20" customWidth="1" style="13" min="14" max="14"/>
+    <col width="20" customWidth="1" style="13" min="15" max="15"/>
+    <col width="20" customWidth="1" style="13" min="16" max="16"/>
+    <col width="20" customWidth="1" style="13" min="17" max="17"/>
+    <col width="20" customWidth="1" style="13" min="18" max="18"/>
+    <col width="20" customWidth="1" style="13" min="19" max="19"/>
+    <col width="20" customWidth="1" style="13" min="20" max="20"/>
+    <col width="20" customWidth="1" style="13" min="21" max="21"/>
+    <col width="20" customWidth="1" style="13" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -54475,14 +54567,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="13">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="13">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>model</t>
@@ -54591,6 +54684,16 @@
       <c r="V4" s="14" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -54656,6 +54759,12 @@
       <c r="V5" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -54728,6 +54837,12 @@
       <c r="V6" s="15" t="n">
         <v>0.9515593841782986</v>
       </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -54800,6 +54915,12 @@
       <c r="V7" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -54872,6 +54993,12 @@
       <c r="V8" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -54891,10 +55018,10 @@
         <v>10</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>4.577821514309684</v>
@@ -54943,6 +55070,12 @@
       </c>
       <c r="V9" s="15" t="n">
         <v>4.505329171349933</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="10">
@@ -54963,10 +55096,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>23.08353417746487</v>
+        <v>17.5405588673282</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>15.90255241749527</v>
@@ -55015,6 +55148,12 @@
       </c>
       <c r="V10" s="15" t="n">
         <v>59.77915649033152</v>
+      </c>
+      <c r="W10" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X10" t="n">
+        <v>18.26147259967061</v>
       </c>
     </row>
     <row r="11">
@@ -55035,10 +55174,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>5.280025044025574</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>4.253960143076137</v>
@@ -55087,6 +55226,12 @@
       </c>
       <c r="V11" s="15" t="n">
         <v>4.076903184343629</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="12">
@@ -55107,10 +55252,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>27.87866446553727</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>35.33173047665775</v>
@@ -55159,6 +55304,12 @@
       </c>
       <c r="V12" s="15" t="n">
         <v>35.71211791968918</v>
+      </c>
+      <c r="W12" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22.05491859863601</v>
       </c>
     </row>
     <row r="13">
@@ -55179,10 +55330,10 @@
         <v>192.1678373016385</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>44.69612244609182</v>
+        <v>32.66594692768881</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>82.34673248644883</v>
+        <v>52.72727295358897</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>2095.248025656152</v>
@@ -55231,6 +55382,12 @@
       </c>
       <c r="V13" s="15" t="n">
         <v>14877.93741284232</v>
+      </c>
+      <c r="W13" t="n">
+        <v>34.20335794997818</v>
+      </c>
+      <c r="X13" t="n">
+        <v>56.22377819574023</v>
       </c>
     </row>
     <row r="14">
@@ -55251,10 +55408,10 @@
         <v>957.3100822228713</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>142.6316473278907</v>
+        <v>94.72342790053084</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>119.6790259721415</v>
+        <v>79.26175744474504</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>66.85909344832929</v>
@@ -55303,6 +55460,12 @@
       </c>
       <c r="V14" s="15" t="n">
         <v>273.2189846219271</v>
+      </c>
+      <c r="W14" t="n">
+        <v>100.5843105009133</v>
+      </c>
+      <c r="X14" t="n">
+        <v>84.19886949576215</v>
       </c>
     </row>
     <row r="15">
@@ -55323,10 +55486,10 @@
         <v>95.89664212630589</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>27.04720839963061</v>
+        <v>20.6038616514508</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>56.07159249521006</v>
+        <v>37.70118799536801</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>87.69028664784985</v>
@@ -55375,6 +55538,12 @@
       </c>
       <c r="V15" s="15" t="n">
         <v>203.4330067474349</v>
+      </c>
+      <c r="W15" t="n">
+        <v>21.44281722434658</v>
+      </c>
+      <c r="X15" t="n">
+        <v>39.93433564550757</v>
       </c>
     </row>
     <row r="16">
@@ -55395,10 +55564,10 @@
         <v>803.5261221856176</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>125.6774988481667</v>
+        <v>84.34008081145512</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>112.9513560225056</v>
+        <v>75.07568037774374</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>125.8278976901746</v>
@@ -55447,6 +55616,12 @@
       </c>
       <c r="V16" s="15" t="n">
         <v>471.8097034434562</v>
+      </c>
+      <c r="W16" t="n">
+        <v>89.42144416594054</v>
+      </c>
+      <c r="X16" t="n">
+        <v>79.70868801149217</v>
       </c>
     </row>
     <row r="17">
@@ -55467,10 +55642,10 @@
         <v>433.072663830632</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>80.40326471437805</v>
+        <v>55.98311339669585</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>90.8347559055665</v>
+        <v>60.95093876890394</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>595.980810547916</v>
@@ -55519,6 +55694,12 @@
       </c>
       <c r="V17" s="15" t="n">
         <v>1722.34384103534</v>
+      </c>
+      <c r="W17" t="n">
+        <v>59.0359960319099</v>
+      </c>
+      <c r="X17" t="n">
+        <v>64.61365241945592</v>
       </c>
     </row>
     <row r="18">
@@ -55539,10 +55720,10 @@
         <v>148.9361077710915</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>37.17816837124528</v>
+        <v>27.58755563311879</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>44.67286555238029</v>
+        <v>31.8383297901462</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>62.99526927008372</v>
@@ -55591,6 +55772,12 @@
       </c>
       <c r="V18" s="15" t="n">
         <v>121.8463895038143</v>
+      </c>
+      <c r="W18" t="n">
+        <v>28.82163947920901</v>
+      </c>
+      <c r="X18" t="n">
+        <v>33.45014159768149</v>
       </c>
     </row>
     <row r="19">
@@ -55611,10 +55798,10 @@
         <v>100.4615790278394</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>27.97159534955067</v>
+        <v>21.24902966393597</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>31.85962489709726</v>
+        <v>23.64253547366279</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>94.46318860159323</v>
@@ -55663,6 +55850,12 @@
       </c>
       <c r="V19" s="15" t="n">
         <v>94.42462805535909</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.12325191669997</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24.69537328805766</v>
       </c>
     </row>
     <row r="20">
@@ -55683,10 +55876,10 @@
         <v>458.5494665163353</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>83.79409714898284</v>
+        <v>58.14554747625077</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>218.4235569116157</v>
+        <v>128.9663065620963</v>
       </c>
       <c r="G20" s="15" t="n">
         <v>526.4921571234207</v>
@@ -55735,6 +55928,12 @@
       </c>
       <c r="V20" s="15" t="n">
         <v>6233.035289922082</v>
+      </c>
+      <c r="W20" t="n">
+        <v>61.34701549533092</v>
+      </c>
+      <c r="X20" t="n">
+        <v>139.2690881142819</v>
       </c>
     </row>
     <row r="21">
@@ -55755,10 +55954,10 @@
         <v>1149.569644128419</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>162.7994465457392</v>
+        <v>106.9436311896749</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>419.1319331031422</v>
+        <v>227.6776140763192</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>2742.0026218271</v>
@@ -55807,6 +56006,12 @@
       </c>
       <c r="V21" s="15" t="n">
         <v>1095224.597367184</v>
+      </c>
+      <c r="W21" t="n">
+        <v>113.7425428506414</v>
+      </c>
+      <c r="X21" t="n">
+        <v>248.6773298608114</v>
       </c>
     </row>
     <row r="22">
@@ -55827,10 +56032,10 @@
         <v>233.2433400524923</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>51.41196048219524</v>
+        <v>37.14266240597716</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>126.5194176558155</v>
+        <v>75.84076780880021</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>324.1174761836669</v>
@@ -55879,6 +56084,12 @@
       </c>
       <c r="V22" s="15" t="n">
         <v>2786.139764177064</v>
+      </c>
+      <c r="W22" t="n">
+        <v>38.95671499956013</v>
+      </c>
+      <c r="X22" t="n">
+        <v>81.61491907909036</v>
       </c>
     </row>
     <row r="23">
@@ -55899,10 +56110,10 @@
         <v>707.6563663686329</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>114.6526832161108</v>
+        <v>77.52663157506882</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>277.5429147385729</v>
+        <v>159.3851682131666</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>7317.526805497487</v>
@@ -55951,6 +56162,12 @@
       </c>
       <c r="V23" s="15" t="n">
         <v>1645094.341484428</v>
+      </c>
+      <c r="W23" t="n">
+        <v>82.1062067044645</v>
+      </c>
+      <c r="X23" t="n">
+        <v>172.7159821560637</v>
       </c>
     </row>
     <row r="24">
@@ -55971,10 +56188,10 @@
         <v>14.25607593602188</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>6.822160362509687</v>
+        <v>5.822500744826133</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>9.974089204406337</v>
+        <v>7.886641531625287</v>
       </c>
       <c r="G24" s="15" t="n">
         <v>16.07734930921978</v>
@@ -56023,6 +56240,12 @@
       </c>
       <c r="V24" s="15" t="n">
         <v>23.7201163809729</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5.959401555272611</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.157400780495703</v>
       </c>
     </row>
     <row r="25">
@@ -56043,10 +56266,10 @@
         <v>260.6153549998892</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>55.70427595599621</v>
+        <v>39.97825302781153</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>66.98390168951386</v>
+        <v>45.95644332462776</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>104.2460481282354</v>
@@ -56095,6 +56318,12 @@
       </c>
       <c r="V25" s="15" t="n">
         <v>310.1782655945706</v>
+      </c>
+      <c r="W25" t="n">
+        <v>41.97151006807996</v>
+      </c>
+      <c r="X25" t="n">
+        <v>48.55654078178316</v>
       </c>
     </row>
     <row r="26">
@@ -56115,10 +56344,10 @@
         <v>537.7936739979261</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>94.02452572065314</v>
+        <v>64.62730910556859</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>104.5984655435359</v>
+        <v>68.89654834470186</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>157.1760602802228</v>
@@ -56167,6 +56396,12 @@
       </c>
       <c r="V26" s="15" t="n">
         <v>768.3150282244065</v>
+      </c>
+      <c r="W26" t="n">
+        <v>68.28079088333945</v>
+      </c>
+      <c r="X26" t="n">
+        <v>73.22489200527703</v>
       </c>
     </row>
     <row r="27">
@@ -56187,10 +56422,10 @@
         <v>614.0613855691029</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>103.4813688456822</v>
+        <v>70.56716399283415</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>102.7621261364643</v>
+        <v>68.60061415059394</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>206.6330656441522</v>
@@ -56239,6 +56474,12 @@
       </c>
       <c r="V27" s="15" t="n">
         <v>748.5026573846656</v>
+      </c>
+      <c r="W27" t="n">
+        <v>74.64296450565553</v>
+      </c>
+      <c r="X27" t="n">
+        <v>72.78499931797944</v>
       </c>
     </row>
     <row r="28">
@@ -56259,10 +56500,10 @@
         <v>472.1088760681196</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>85.5773999698382</v>
+        <v>59.279899273387</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>143.4905091038848</v>
+        <v>90.11143273373939</v>
       </c>
       <c r="G28" s="15" t="n">
         <v>948.2646461013878</v>
@@ -56311,6 +56552,12 @@
       </c>
       <c r="V28" s="15" t="n">
         <v>2766.021116765205</v>
+      </c>
+      <c r="W28" t="n">
+        <v>62.55976718436576</v>
+      </c>
+      <c r="X28" t="n">
+        <v>96.42460617606433</v>
       </c>
     </row>
     <row r="29">
@@ -56331,10 +56578,10 @@
         <v>443.19575516822</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>81.75704873945472</v>
+        <v>56.84734670066118</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>137.4895374643425</v>
+        <v>86.18089558214803</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>811.720324648783</v>
@@ -56383,6 +56630,12 @@
       </c>
       <c r="V29" s="15" t="n">
         <v>2351.352010120519</v>
+      </c>
+      <c r="W29" t="n">
+        <v>59.95947384551975</v>
+      </c>
+      <c r="X29" t="n">
+        <v>92.23948616526582</v>
       </c>
     </row>
     <row r="30">
@@ -56403,10 +56656,10 @@
         <v>3690.679934159451</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>378.1981726321904</v>
+        <v>231.747404317973</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>592.0104834453182</v>
+        <v>330.6351772171339</v>
       </c>
       <c r="G30" s="15" t="n">
         <v>0</v>
@@ -56452,6 +56705,12 @@
       </c>
       <c r="V30" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>249.0080859298023</v>
+      </c>
+      <c r="X30" t="n">
+        <v>359.9372982916983</v>
       </c>
     </row>
     <row r="31">
@@ -56472,10 +56731,10 @@
         <v>6316.900158152956</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>557.6747112644658</v>
+        <v>330.9474462171082</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>600.4669169174184</v>
+        <v>342.8897408224037</v>
       </c>
       <c r="G31" s="15" t="n">
         <v>196639.6235546877</v>
@@ -56524,6 +56783,12 @@
       </c>
       <c r="V31" s="15" t="n">
         <v>12867258.24483938</v>
+      </c>
+      <c r="W31" t="n">
+        <v>357.2719697561159</v>
+      </c>
+      <c r="X31" t="n">
+        <v>372.1577950636552</v>
       </c>
     </row>
     <row r="32">
@@ -56544,10 +56809,10 @@
         <v>8002.573841696399</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>661.6285267329362</v>
+        <v>387.1389168651923</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>636.0407247825135</v>
+        <v>363.6412451787915</v>
       </c>
       <c r="G32" s="15" t="n">
         <v>0</v>
@@ -56593,6 +56858,12 @@
       </c>
       <c r="V32" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>418.7985782328224</v>
+      </c>
+      <c r="X32" t="n">
+        <v>394.6609619468547</v>
       </c>
     </row>
     <row r="33">
@@ -56613,10 +56884,10 @@
         <v>2832.954810656827</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>312.4011249072236</v>
+        <v>194.4721790061764</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>519.6938790691926</v>
+        <v>291.1028404040098</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>841359.9861091692</v>
@@ -56665,6 +56936,12 @@
       </c>
       <c r="V33" s="15" t="n">
         <v>1414639309.654173</v>
+      </c>
+      <c r="W33" t="n">
+        <v>208.4737632540628</v>
+      </c>
+      <c r="X33" t="n">
+        <v>316.6996488939066</v>
       </c>
     </row>
     <row r="34">
@@ -56685,10 +56962,10 @@
         <v>652.8956149848666</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>108.1701370776778</v>
+        <v>73.49534453944611</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>269.9290920813721</v>
+        <v>157.3739344485984</v>
       </c>
       <c r="G34" s="15" t="n">
         <v>158437.3698017728</v>
@@ -56737,6 +57014,12 @@
       </c>
       <c r="V34" s="15" t="n">
         <v>484185.117512574</v>
+      </c>
+      <c r="W34" t="n">
+        <v>77.7819763119403</v>
+      </c>
+      <c r="X34" t="n">
+        <v>170.2280375697981</v>
       </c>
     </row>
     <row r="35">
@@ -56801,6 +57084,12 @@
       <c r="V35" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -56873,6 +57162,12 @@
       <c r="V36" s="15" t="n">
         <v>0.8537152806236192</v>
       </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -56892,10 +57187,10 @@
         <v>416.179587813214</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>56.28900254449202</v>
+        <v>73.16902902025888</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>88.59793106865003</v>
+        <v>124.051602358648</v>
       </c>
       <c r="G37" s="15" t="n">
         <v>0</v>
@@ -56941,6 +57236,12 @@
       </c>
       <c r="V37" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>76.0908418656785</v>
+      </c>
+      <c r="X37" t="n">
+        <v>130.495353702711</v>
       </c>
     </row>
     <row r="38">
@@ -56961,10 +57262,10 @@
         <v>357.8589689857071</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>50.88677450113939</v>
+        <v>65.71390752353284</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>78.79467664999078</v>
+        <v>109.0006292271502</v>
       </c>
       <c r="G38" s="15" t="n">
         <v>1974.676817436918</v>
@@ -57013,6 +57314,12 @@
       </c>
       <c r="V38" s="15" t="n">
         <v>50303.53156474263</v>
+      </c>
+      <c r="W38" t="n">
+        <v>68.27106823443432</v>
+      </c>
+      <c r="X38" t="n">
+        <v>114.4546145406711</v>
       </c>
     </row>
     <row r="39">
@@ -57033,10 +57340,10 @@
         <v>199.0673338987186</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>34.38626616103237</v>
+        <v>43.28733232006891</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>45.45142535053177</v>
+        <v>59.41950984806437</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>403.5448329427017</v>
@@ -57085,6 +57392,12 @@
       </c>
       <c r="V39" s="15" t="n">
         <v>388.7214670416733</v>
+      </c>
+      <c r="W39" t="n">
+        <v>44.80088239744686</v>
+      </c>
+      <c r="X39" t="n">
+        <v>61.85648360648175</v>
       </c>
     </row>
     <row r="40">
@@ -57105,10 +57418,10 @@
         <v>19.90673338987186</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>7.380758154301324</v>
+        <v>8.406014400535831</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>9.755812879175473</v>
+        <v>11.53873959620375</v>
       </c>
       <c r="G40" s="15" t="n">
         <v>10.13479730321421</v>
@@ -57157,6 +57470,12 @@
       </c>
       <c r="V40" s="15" t="n">
         <v>9.515134778306953</v>
+      </c>
+      <c r="W40" t="n">
+        <v>8.570844148075091</v>
+      </c>
+      <c r="X40" t="n">
+        <v>11.83374639445339</v>
       </c>
     </row>
     <row r="41">
@@ -57177,10 +57496,10 @@
         <v>174.1521562345644</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>31.44683930314632</v>
+        <v>39.35749816288925</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>33.95247504464749</v>
+        <v>43.88701766727957</v>
       </c>
       <c r="G41" s="15" t="n">
         <v>72.37923796403966</v>
@@ -57229,6 +57548,12 @@
       </c>
       <c r="V41" s="15" t="n">
         <v>2184.01743144918</v>
+      </c>
+      <c r="W41" t="n">
+        <v>40.69829501237073</v>
+      </c>
+      <c r="X41" t="n">
+        <v>45.61090054732936</v>
       </c>
     </row>
     <row r="42">
@@ -57249,10 +57574,10 @@
         <v>98.07449751016838</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>21.42521366403237</v>
+        <v>26.1535868392652</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>17.87446335772178</v>
+        <v>21.83387403064396</v>
       </c>
       <c r="G42" s="15" t="n">
         <v>22.48481592273476</v>
@@ -57301,6 +57626,12 @@
       </c>
       <c r="V42" s="15" t="n">
         <v>377.6757630310734</v>
+      </c>
+      <c r="W42" t="n">
+        <v>26.94393320884064</v>
+      </c>
+      <c r="X42" t="n">
+        <v>22.49596958420992</v>
       </c>
     </row>
     <row r="43">
@@ -57321,10 +57652,10 @@
         <v>10</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>4.658907044799036</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>4.658907044799037</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="G43" s="15" t="n">
         <v>5.046009141842525</v>
@@ -57373,6 +57704,12 @@
       </c>
       <c r="V43" s="15" t="n">
         <v>4.830501414419818</v>
+      </c>
+      <c r="W43" t="n">
+        <v>5.2271260127287</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5.2271260127287</v>
       </c>
     </row>
     <row r="44">
@@ -57444,6 +57781,12 @@
         <v>1</v>
       </c>
       <c r="V44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -57458,31 +57801,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="46" customWidth="1" style="13" min="1" max="1"/>
+    <col width="32" customWidth="1" style="13" min="2" max="2"/>
+    <col width="20" customWidth="1" style="13" min="3" max="3"/>
+    <col width="20" customWidth="1" style="13" min="4" max="4"/>
+    <col width="20" customWidth="1" style="13" min="5" max="5"/>
+    <col width="20" customWidth="1" style="13" min="6" max="6"/>
+    <col width="20" customWidth="1" style="13" min="7" max="7"/>
+    <col width="20" customWidth="1" style="13" min="8" max="8"/>
+    <col width="20" customWidth="1" style="13" min="9" max="9"/>
+    <col width="20" customWidth="1" style="13" min="10" max="10"/>
+    <col width="20" customWidth="1" style="13" min="11" max="11"/>
+    <col width="20" customWidth="1" style="13" min="12" max="12"/>
+    <col width="20" customWidth="1" style="13" min="13" max="13"/>
+    <col width="20" customWidth="1" style="13" min="14" max="14"/>
+    <col width="20" customWidth="1" style="13" min="15" max="15"/>
+    <col width="20" customWidth="1" style="13" min="16" max="16"/>
+    <col width="20" customWidth="1" style="13" min="17" max="17"/>
+    <col width="20" customWidth="1" style="13" min="18" max="18"/>
+    <col width="20" customWidth="1" style="13" min="19" max="19"/>
+    <col width="20" customWidth="1" style="13" min="20" max="20"/>
+    <col width="20" customWidth="1" style="13" min="21" max="21"/>
+    <col width="20" customWidth="1" style="13" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -57492,14 +57835,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="13">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="13">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>model</t>
@@ -57608,6 +57952,16 @@
       <c r="V4" s="14" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -57664,6 +58018,9 @@
       <c r="V5" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -57727,6 +58084,9 @@
       <c r="V6" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -57790,6 +58150,9 @@
       <c r="V7" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -57853,6 +58216,9 @@
       <c r="V8" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -57866,7 +58232,7 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>2.640012522012788</v>
+        <v>2.301317548697287</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>2.288910757154842</v>
@@ -57915,6 +58281,9 @@
       </c>
       <c r="V9" s="15" t="n">
         <v>2.308357824368465</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.348133226556577</v>
       </c>
     </row>
     <row r="10">
@@ -57929,7 +58298,7 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>11.54176708873243</v>
+        <v>8.770279433664099</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>7.951276208747637</v>
@@ -57978,6 +58347,9 @@
       </c>
       <c r="V10" s="15" t="n">
         <v>30.57866372023318</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.130736299835307</v>
       </c>
     </row>
     <row r="11">
@@ -57992,7 +58364,7 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>1.584007513207673</v>
+        <v>1.380790529218372</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>1.276188042922841</v>
@@ -58041,6 +58413,9 @@
       </c>
       <c r="V11" s="15" t="n">
         <v>1.266223979894226</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.408879935933946</v>
       </c>
     </row>
     <row r="12">
@@ -58055,7 +58430,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>8.363599339661182</v>
+        <v>6.355274951930507</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>10.59951914299733</v>
@@ -58104,6 +58479,9 @@
       </c>
       <c r="V12" s="15" t="n">
         <v>11.09067603768777</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6.616475579590803</v>
       </c>
     </row>
     <row r="13">
@@ -58118,7 +58496,7 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>36.02567822214979</v>
+        <v>23.20128201514521</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>884.2654320712849</v>
@@ -58167,6 +58545,9 @@
       </c>
       <c r="V13" s="15" t="n">
         <v>6957.067696845485</v>
+      </c>
+      <c r="X13" t="n">
+        <v>24.71678057998663</v>
       </c>
     </row>
     <row r="14">
@@ -58181,7 +58562,7 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>59.81536868923033</v>
+        <v>39.61273764012287</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>33.41168652260096</v>
@@ -58230,6 +58611,9 @@
       </c>
       <c r="V14" s="15" t="n">
         <v>139.2881081991169</v>
+      </c>
+      <c r="X14" t="n">
+        <v>42.08051921752429</v>
       </c>
     </row>
     <row r="15">
@@ -58244,7 +58628,7 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>20.71216352040432</v>
+        <v>13.67204278942812</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>30.29551595789478</v>
@@ -58293,6 +58677,9 @@
       </c>
       <c r="V15" s="15" t="n">
         <v>84.73603667840504</v>
+      </c>
+      <c r="X15" t="n">
+        <v>14.52095528725243</v>
       </c>
     </row>
     <row r="16">
@@ -58307,7 +58694,7 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>56.44779934678724</v>
+        <v>37.51665593903211</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>62.87784335837292</v>
@@ -58356,6 +58743,9 @@
       </c>
       <c r="V16" s="15" t="n">
         <v>241.3358580441285</v>
+      </c>
+      <c r="X16" t="n">
+        <v>39.83228908714745</v>
       </c>
     </row>
     <row r="17">
@@ -58370,7 +58760,7 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>43.73710722116262</v>
+        <v>29.36248397311394</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>279.5808728436076</v>
@@ -58419,6 +58809,9 @@
       </c>
       <c r="V17" s="15" t="n">
         <v>862.9555412761928</v>
+      </c>
+      <c r="X17" t="n">
+        <v>31.12452475130046</v>
       </c>
     </row>
     <row r="18">
@@ -58433,7 +58826,7 @@
         </is>
       </c>
       <c r="F18" s="15" t="n">
-        <v>21.71819258058765</v>
+        <v>15.50965073341023</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>30.15162213949722</v>
@@ -58482,6 +58875,9 @@
       </c>
       <c r="V18" s="15" t="n">
         <v>61.00638723800488</v>
+      </c>
+      <c r="X18" t="n">
+        <v>16.2900525466089</v>
       </c>
     </row>
     <row r="19">
@@ -58496,7 +58892,7 @@
         </is>
       </c>
       <c r="F19" s="15" t="n">
-        <v>9.616408807162506</v>
+        <v>7.118261812800782</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>28.40809628866194</v>
@@ -58545,6 +58941,9 @@
       </c>
       <c r="V19" s="15" t="n">
         <v>30.16948865601263</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.438017530134218</v>
       </c>
     </row>
     <row r="20">
@@ -58559,7 +58958,7 @@
         </is>
       </c>
       <c r="F20" s="15" t="n">
-        <v>100.6275767200453</v>
+        <v>58.89036939034452</v>
       </c>
       <c r="G20" s="15" t="n">
         <v>239.4045354224563</v>
@@ -58608,6 +59007,9 @@
       </c>
       <c r="V20" s="15" t="n">
         <v>3060.457117583493</v>
+      </c>
+      <c r="X20" t="n">
+        <v>63.68512433122689</v>
       </c>
     </row>
     <row r="21">
@@ -58622,7 +59024,7 @@
         </is>
       </c>
       <c r="F21" s="15" t="n">
-        <v>172.7316893504228</v>
+        <v>92.13356560330777</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>1178.766857505088</v>
@@ -58671,6 +59073,9 @@
       </c>
       <c r="V21" s="15" t="n">
         <v>534048.733202767</v>
+      </c>
+      <c r="X21" t="n">
+        <v>100.8996397181391</v>
       </c>
     </row>
     <row r="22">
@@ -58685,7 +59090,7 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>49.01983518812542</v>
+        <v>28.39083270025337</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>132.9170707658792</v>
@@ -58734,6 +59139,9 @@
       </c>
       <c r="V22" s="15" t="n">
         <v>1351.256347786268</v>
+      </c>
+      <c r="X22" t="n">
+        <v>30.70676707937115</v>
       </c>
     </row>
     <row r="23">
@@ -58748,7 +59156,7 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>117.5248709126216</v>
+        <v>66.69950310700396</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>3170.705077828824</v>
@@ -58797,6 +59205,9 @@
       </c>
       <c r="V23" s="15" t="n">
         <v>802390.1492857393</v>
+      </c>
+      <c r="X23" t="n">
+        <v>72.40288537481295</v>
       </c>
     </row>
     <row r="24">
@@ -58811,7 +59222,7 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>7.265375408700205</v>
+        <v>5.929357810338402</v>
       </c>
       <c r="G24" s="15" t="n">
         <v>12.16148356265587</v>
@@ -58860,6 +59271,9 @@
       </c>
       <c r="V24" s="15" t="n">
         <v>16.2610545606418</v>
+      </c>
+      <c r="X24" t="n">
+        <v>6.105139364766177</v>
       </c>
     </row>
     <row r="25">
@@ -58874,7 +59288,7 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>33.30237592639127</v>
+        <v>22.83416876340346</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>51.79800239026467</v>
@@ -58923,6 +59337,9 @@
       </c>
       <c r="V25" s="15" t="n">
         <v>158.3505104971605</v>
+      </c>
+      <c r="X25" t="n">
+        <v>24.12829694442085</v>
       </c>
     </row>
     <row r="26">
@@ -58937,7 +59354,7 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>51.91984428226138</v>
+        <v>34.2328999822808</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>72.51717521560929</v>
@@ -58986,6 +59403,9 @@
       </c>
       <c r="V26" s="15" t="n">
         <v>371.5681739455553</v>
+      </c>
+      <c r="X26" t="n">
+        <v>36.37855880332653</v>
       </c>
     </row>
     <row r="27">
@@ -59000,7 +59420,7 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>51.22189621877343</v>
+        <v>34.18501237167529</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>102.8169274632543</v>
@@ -59049,6 +59469,9 @@
       </c>
       <c r="V27" s="15" t="n">
         <v>382.4625627660487</v>
+      </c>
+      <c r="X27" t="n">
+        <v>36.27170578623455</v>
       </c>
     </row>
     <row r="28">
@@ -59063,7 +59486,7 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>67.99412458235994</v>
+        <v>42.6336945997876</v>
       </c>
       <c r="G28" s="15" t="n">
         <v>443.3693273898904</v>
@@ -59112,6 +59535,9 @@
       </c>
       <c r="V28" s="15" t="n">
         <v>1380.632097213146</v>
+      </c>
+      <c r="X28" t="n">
+        <v>45.63004396712611</v>
       </c>
     </row>
     <row r="29">
@@ -59126,7 +59552,7 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>68.04311735299089</v>
+        <v>42.6799212343863</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>389.0726358640387</v>
@@ -59175,6 +59601,9 @@
       </c>
       <c r="V29" s="15" t="n">
         <v>1186.451320717368</v>
+      </c>
+      <c r="X29" t="n">
+        <v>45.67550971275495</v>
       </c>
     </row>
     <row r="30">
@@ -59189,7 +59618,7 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>283.2340067207638</v>
+        <v>158.0509570120881</v>
       </c>
       <c r="G30" s="15" t="n">
         <v>0</v>
@@ -59235,6 +59664,9 @@
       </c>
       <c r="V30" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>172.0770587541016</v>
       </c>
     </row>
     <row r="31">
@@ -59249,7 +59681,7 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>297.3783312139415</v>
+        <v>169.8965085776798</v>
       </c>
       <c r="G31" s="15" t="n">
         <v>92060.3101393988</v>
@@ -59298,6 +59730,9 @@
       </c>
       <c r="V31" s="15" t="n">
         <v>6283035.907771785</v>
+      </c>
+      <c r="X31" t="n">
+        <v>184.3868194370353</v>
       </c>
     </row>
     <row r="32">
@@ -59312,7 +59747,7 @@
         </is>
       </c>
       <c r="F32" s="15" t="n">
-        <v>313.6708876428777</v>
+        <v>179.2080128235593</v>
       </c>
       <c r="G32" s="15" t="n">
         <v>0</v>
@@ -59358,6 +59793,9 @@
       </c>
       <c r="V32" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>194.5175804729221</v>
       </c>
     </row>
     <row r="33">
@@ -59372,7 +59810,7 @@
         </is>
       </c>
       <c r="F33" s="15" t="n">
-        <v>238.773215910952</v>
+        <v>133.0271993512209</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>390249.6304845259</v>
@@ -59421,6 +59859,9 @@
       </c>
       <c r="V33" s="15" t="n">
         <v>693202949.0927888</v>
+      </c>
+      <c r="X33" t="n">
+        <v>144.8413364228488</v>
       </c>
     </row>
     <row r="34">
@@ -59435,7 +59876,7 @@
         </is>
       </c>
       <c r="F34" s="15" t="n">
-        <v>131.4271511380308</v>
+        <v>76.60972450076972</v>
       </c>
       <c r="G34" s="15" t="n">
         <v>74951.29476335137</v>
@@ -59484,6 +59925,9 @@
       </c>
       <c r="V34" s="15" t="n">
         <v>242675.1433360545</v>
+      </c>
+      <c r="X34" t="n">
+        <v>82.86840722828065</v>
       </c>
     </row>
     <row r="35">
@@ -59539,6 +59983,9 @@
       <c r="V35" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -59602,6 +60049,9 @@
       <c r="V36" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -59615,7 +60065,7 @@
         </is>
       </c>
       <c r="F37" s="15" t="n">
-        <v>48.18043942955434</v>
+        <v>67.66369465845605</v>
       </c>
       <c r="G37" s="15" t="n">
         <v>0</v>
@@ -59661,6 +60111,9 @@
       </c>
       <c r="V37" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>71.20850372013344</v>
       </c>
     </row>
     <row r="38">
@@ -59675,7 +60128,7 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>32.98942136158241</v>
+        <v>46.71486371866341</v>
       </c>
       <c r="G38" s="15" t="n">
         <v>794.0613257489242</v>
@@ -59724,6 +60177,9 @@
       </c>
       <c r="V38" s="15" t="n">
         <v>26947.97573917317</v>
+      </c>
+      <c r="X38" t="n">
+        <v>49.21670440158326</v>
       </c>
     </row>
     <row r="39">
@@ -59738,7 +60194,7 @@
         </is>
       </c>
       <c r="F39" s="15" t="n">
-        <v>16.84141275334834</v>
+        <v>22.74251350402013</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>153.4693810067471</v>
@@ -59787,6 +60243,9 @@
       </c>
       <c r="V39" s="15" t="n">
         <v>163.9617961193308</v>
+      </c>
+      <c r="X39" t="n">
+        <v>23.78566475037847</v>
       </c>
     </row>
     <row r="40">
@@ -59801,7 +60260,7 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>3.614884905709641</v>
+        <v>4.41639356765216</v>
       </c>
       <c r="G40" s="15" t="n">
         <v>3.85429558696389</v>
@@ -59850,6 +60309,9 @@
       </c>
       <c r="V40" s="15" t="n">
         <v>4.021840113462793</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.550428800158525</v>
       </c>
     </row>
     <row r="41">
@@ -59864,7 +60326,7 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>18.89248698205429</v>
+        <v>24.42180522907254</v>
       </c>
       <c r="G41" s="15" t="n">
         <v>40.27526191934068</v>
@@ -59913,6 +60375,9 @@
       </c>
       <c r="V41" s="15" t="n">
         <v>1197.692607212351</v>
+      </c>
+      <c r="X41" t="n">
+        <v>25.38130195482818</v>
       </c>
     </row>
     <row r="42">
@@ -59927,7 +60392,7 @@
         </is>
       </c>
       <c r="F42" s="15" t="n">
-        <v>9.93791101168336</v>
+        <v>12.14138967428119</v>
       </c>
       <c r="G42" s="15" t="n">
         <v>12.50294208253858</v>
@@ -59976,6 +60441,9 @@
       </c>
       <c r="V42" s="15" t="n">
         <v>209.5592222512306</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12.5098744940813</v>
       </c>
     </row>
     <row r="43">
@@ -59990,7 +60458,7 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>2.595011223953063</v>
+        <v>2.868308683927719</v>
       </c>
       <c r="G43" s="15" t="n">
         <v>2.810627092006287</v>
@@ -60039,6 +60507,9 @@
       </c>
       <c r="V43" s="15" t="n">
         <v>2.875704343664626</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.911509189089886</v>
       </c>
     </row>
     <row r="44">
@@ -60101,6 +60572,9 @@
         <v>1</v>
       </c>
       <c r="V44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -60118,15 +60592,15 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="90" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" style="13" min="1" max="1"/>
+    <col width="32" customWidth="1" style="13" min="2" max="2"/>
+    <col width="20" customWidth="1" style="13" min="3" max="3"/>
+    <col width="20" customWidth="1" style="13" min="4" max="4"/>
+    <col width="20" customWidth="1" style="13" min="5" max="5"/>
+    <col width="20" customWidth="1" style="13" min="6" max="6"/>
+    <col width="20" customWidth="1" style="13" min="7" max="7"/>
+    <col width="20" customWidth="1" style="13" min="8" max="8"/>
+    <col width="90" customWidth="1" style="13" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -60136,14 +60610,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="13">
+      <c r="A2" t="inlineStr">
         <is>
           <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="13">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>model</t>
@@ -60426,78 +60901,78 @@
   <dimension ref="A1:BT135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="14" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="14" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-    <col width="14" customWidth="1" min="63" max="63"/>
-    <col width="14" customWidth="1" min="64" max="64"/>
-    <col width="14" customWidth="1" min="65" max="65"/>
-    <col width="14" customWidth="1" min="66" max="66"/>
-    <col width="14" customWidth="1" min="67" max="67"/>
-    <col width="14" customWidth="1" min="68" max="68"/>
-    <col width="14" customWidth="1" min="69" max="69"/>
-    <col width="14" customWidth="1" min="70" max="70"/>
-    <col width="14" customWidth="1" min="71" max="71"/>
-    <col width="14" customWidth="1" min="72" max="72"/>
+    <col width="26" customWidth="1" style="13" min="1" max="1"/>
+    <col width="22" customWidth="1" style="13" min="2" max="2"/>
+    <col width="14" customWidth="1" style="13" min="3" max="3"/>
+    <col width="14" customWidth="1" style="13" min="4" max="4"/>
+    <col width="14" customWidth="1" style="13" min="5" max="5"/>
+    <col width="14" customWidth="1" style="13" min="6" max="6"/>
+    <col width="14" customWidth="1" style="13" min="7" max="7"/>
+    <col width="14" customWidth="1" style="13" min="8" max="8"/>
+    <col width="14" customWidth="1" style="13" min="9" max="9"/>
+    <col width="14" customWidth="1" style="13" min="10" max="10"/>
+    <col width="14" customWidth="1" style="13" min="11" max="11"/>
+    <col width="14" customWidth="1" style="13" min="12" max="12"/>
+    <col width="14" customWidth="1" style="13" min="13" max="13"/>
+    <col width="14" customWidth="1" style="13" min="14" max="14"/>
+    <col width="14" customWidth="1" style="13" min="15" max="15"/>
+    <col width="14" customWidth="1" style="13" min="16" max="16"/>
+    <col width="14" customWidth="1" style="13" min="17" max="17"/>
+    <col width="14" customWidth="1" style="13" min="18" max="18"/>
+    <col width="14" customWidth="1" style="13" min="19" max="19"/>
+    <col width="14" customWidth="1" style="13" min="20" max="20"/>
+    <col width="14" customWidth="1" style="13" min="21" max="21"/>
+    <col width="14" customWidth="1" style="13" min="22" max="22"/>
+    <col width="14" customWidth="1" style="13" min="23" max="23"/>
+    <col width="14" customWidth="1" style="13" min="24" max="24"/>
+    <col width="14" customWidth="1" style="13" min="25" max="25"/>
+    <col width="14" customWidth="1" style="13" min="26" max="26"/>
+    <col width="14" customWidth="1" style="13" min="27" max="27"/>
+    <col width="14" customWidth="1" style="13" min="28" max="28"/>
+    <col width="14" customWidth="1" style="13" min="29" max="29"/>
+    <col width="14" customWidth="1" style="13" min="30" max="30"/>
+    <col width="14" customWidth="1" style="13" min="31" max="31"/>
+    <col width="14" customWidth="1" style="13" min="32" max="32"/>
+    <col width="14" customWidth="1" style="13" min="33" max="33"/>
+    <col width="14" customWidth="1" style="13" min="34" max="34"/>
+    <col width="14" customWidth="1" style="13" min="35" max="35"/>
+    <col width="14" customWidth="1" style="13" min="36" max="36"/>
+    <col width="14" customWidth="1" style="13" min="37" max="37"/>
+    <col width="14" customWidth="1" style="13" min="38" max="38"/>
+    <col width="14" customWidth="1" style="13" min="39" max="39"/>
+    <col width="14" customWidth="1" style="13" min="40" max="40"/>
+    <col width="14" customWidth="1" style="13" min="41" max="41"/>
+    <col width="14" customWidth="1" style="13" min="42" max="42"/>
+    <col width="14" customWidth="1" style="13" min="43" max="43"/>
+    <col width="14" customWidth="1" style="13" min="44" max="44"/>
+    <col width="14" customWidth="1" style="13" min="45" max="45"/>
+    <col width="14" customWidth="1" style="13" min="46" max="46"/>
+    <col width="14" customWidth="1" style="13" min="47" max="47"/>
+    <col width="14" customWidth="1" style="13" min="48" max="48"/>
+    <col width="14" customWidth="1" style="13" min="49" max="49"/>
+    <col width="14" customWidth="1" style="13" min="50" max="50"/>
+    <col width="14" customWidth="1" style="13" min="51" max="51"/>
+    <col width="14" customWidth="1" style="13" min="52" max="52"/>
+    <col width="14" customWidth="1" style="13" min="53" max="53"/>
+    <col width="14" customWidth="1" style="13" min="54" max="54"/>
+    <col width="14" customWidth="1" style="13" min="55" max="55"/>
+    <col width="14" customWidth="1" style="13" min="56" max="56"/>
+    <col width="14" customWidth="1" style="13" min="57" max="57"/>
+    <col width="14" customWidth="1" style="13" min="58" max="58"/>
+    <col width="14" customWidth="1" style="13" min="59" max="59"/>
+    <col width="14" customWidth="1" style="13" min="60" max="60"/>
+    <col width="14" customWidth="1" style="13" min="61" max="61"/>
+    <col width="14" customWidth="1" style="13" min="62" max="62"/>
+    <col width="14" customWidth="1" style="13" min="63" max="63"/>
+    <col width="14" customWidth="1" style="13" min="64" max="64"/>
+    <col width="14" customWidth="1" style="13" min="65" max="65"/>
+    <col width="14" customWidth="1" style="13" min="66" max="66"/>
+    <col width="14" customWidth="1" style="13" min="67" max="67"/>
+    <col width="14" customWidth="1" style="13" min="68" max="68"/>
+    <col width="14" customWidth="1" style="13" min="69" max="69"/>
+    <col width="14" customWidth="1" style="13" min="70" max="70"/>
+    <col width="14" customWidth="1" style="13" min="71" max="71"/>
+    <col width="14" customWidth="1" style="13" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -60585,6 +61060,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
